--- a/raw/Timetable_2026Autumn_2025IE.xlsx
+++ b/raw/Timetable_2026Autumn_2025IE.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30425"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C812BF72-BFF0-4138-8224-7B472CCE58EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8988D75C-C13E-48B5-93E8-8A975F9210DD}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2025IE1" sheetId="2" r:id="rId1"/>
@@ -184,7 +184,7 @@
     <t>8       Sep.</t>
   </si>
   <si>
-    <t>B405</t>
+    <t>B409</t>
   </si>
   <si>
     <t>9       Sep.</t>
@@ -684,7 +684,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -854,11 +854,88 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1056,6 +1133,66 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1405,81 +1542,81 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="54" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="55" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="56"/>
-      <c r="D2" s="45" t="s">
+      <c r="D2" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45" t="s">
+      <c r="E2" s="68"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45" t="s">
+      <c r="H2" s="68"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="45" t="s">
+      <c r="K2" s="68"/>
+      <c r="L2" s="69"/>
+      <c r="M2" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="45"/>
-      <c r="O2" s="45"/>
-      <c r="P2" s="45" t="s">
+      <c r="N2" s="68"/>
+      <c r="O2" s="69"/>
+      <c r="P2" s="67" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="45"/>
-      <c r="R2" s="45"/>
-      <c r="S2" s="45" t="s">
+      <c r="Q2" s="68"/>
+      <c r="R2" s="69"/>
+      <c r="S2" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="T2" s="45"/>
-      <c r="U2" s="45"/>
+      <c r="T2" s="68"/>
+      <c r="U2" s="69"/>
     </row>
     <row r="3" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="45"/>
-      <c r="B3" s="57"/>
+      <c r="A3" s="71"/>
+      <c r="B3" s="70"/>
       <c r="C3" s="58"/>
-      <c r="D3" s="54" t="s">
+      <c r="D3" s="67" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="45" t="s">
+      <c r="E3" s="68"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45" t="s">
+      <c r="H3" s="68"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="45"/>
-      <c r="L3" s="45"/>
-      <c r="M3" s="45" t="s">
+      <c r="K3" s="68"/>
+      <c r="L3" s="69"/>
+      <c r="M3" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="45"/>
-      <c r="O3" s="45"/>
-      <c r="P3" s="45" t="s">
+      <c r="N3" s="68"/>
+      <c r="O3" s="69"/>
+      <c r="P3" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="45"/>
-      <c r="R3" s="45"/>
-      <c r="S3" s="45" t="s">
+      <c r="Q3" s="68"/>
+      <c r="R3" s="69"/>
+      <c r="S3" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="45"/>
-      <c r="U3" s="45"/>
+      <c r="T3" s="68"/>
+      <c r="U3" s="69"/>
     </row>
     <row r="4" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="46">
+      <c r="A4" s="79">
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -1537,7 +1674,7 @@
       </c>
     </row>
     <row r="5" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A5" s="46"/>
+      <c r="A5" s="80"/>
       <c r="B5" s="2" t="s">
         <v>23</v>
       </c>
@@ -1583,7 +1720,7 @@
       </c>
     </row>
     <row r="6" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="46"/>
+      <c r="A6" s="80"/>
       <c r="B6" s="2" t="s">
         <v>25</v>
       </c>
@@ -1645,7 +1782,7 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="46"/>
+      <c r="A7" s="80"/>
       <c r="B7" s="2" t="s">
         <v>31</v>
       </c>
@@ -1709,7 +1846,7 @@
       </c>
     </row>
     <row r="8" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A8" s="46"/>
+      <c r="A8" s="80"/>
       <c r="B8" s="2" t="s">
         <v>36</v>
       </c>
@@ -1753,7 +1890,7 @@
       </c>
     </row>
     <row r="9" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="46"/>
+      <c r="A9" s="80"/>
       <c r="B9" s="2" t="s">
         <v>39</v>
       </c>
@@ -1797,7 +1934,7 @@
       </c>
     </row>
     <row r="10" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A10" s="46"/>
+      <c r="A10" s="81"/>
       <c r="B10" s="2" t="s">
         <v>43</v>
       </c>
@@ -1839,7 +1976,7 @@
       </c>
     </row>
     <row r="11" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A11" s="53">
+      <c r="A11" s="72">
         <v>2</v>
       </c>
       <c r="B11" s="13" t="s">
@@ -1905,7 +2042,7 @@
       </c>
     </row>
     <row r="12" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="53"/>
+      <c r="A12" s="73"/>
       <c r="B12" s="13" t="s">
         <v>47</v>
       </c>
@@ -1967,7 +2104,7 @@
       </c>
     </row>
     <row r="13" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="53"/>
+      <c r="A13" s="73"/>
       <c r="B13" s="13" t="s">
         <v>49</v>
       </c>
@@ -2019,7 +2156,7 @@
       <c r="AA13" s="3"/>
     </row>
     <row r="14" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="53"/>
+      <c r="A14" s="73"/>
       <c r="B14" s="13" t="s">
         <v>50</v>
       </c>
@@ -2083,7 +2220,7 @@
       <c r="AA14" s="3"/>
     </row>
     <row r="15" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="53"/>
+      <c r="A15" s="73"/>
       <c r="B15" s="13" t="s">
         <v>54</v>
       </c>
@@ -2135,7 +2272,7 @@
       <c r="AA15" s="3"/>
     </row>
     <row r="16" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="53"/>
+      <c r="A16" s="73"/>
       <c r="B16" s="13" t="s">
         <v>55</v>
       </c>
@@ -2162,7 +2299,7 @@
       <c r="U16" s="17"/>
     </row>
     <row r="17" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A17" s="53"/>
+      <c r="A17" s="74"/>
       <c r="B17" s="13" t="s">
         <v>56</v>
       </c>
@@ -2189,7 +2326,7 @@
       <c r="U17" s="17"/>
     </row>
     <row r="18" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A18" s="46">
+      <c r="A18" s="79">
         <v>3</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -2238,7 +2375,7 @@
       <c r="U18" s="6"/>
     </row>
     <row r="19" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A19" s="46"/>
+      <c r="A19" s="80"/>
       <c r="B19" s="2" t="s">
         <v>58</v>
       </c>
@@ -2285,7 +2422,7 @@
       <c r="U19" s="6"/>
     </row>
     <row r="20" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A20" s="46"/>
+      <c r="A20" s="80"/>
       <c r="B20" s="2" t="s">
         <v>59</v>
       </c>
@@ -2332,7 +2469,7 @@
       <c r="U20" s="6"/>
     </row>
     <row r="21" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A21" s="46"/>
+      <c r="A21" s="80"/>
       <c r="B21" s="2" t="s">
         <v>60</v>
       </c>
@@ -2391,7 +2528,7 @@
       </c>
     </row>
     <row r="22" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A22" s="46"/>
+      <c r="A22" s="80"/>
       <c r="B22" s="2" t="s">
         <v>61</v>
       </c>
@@ -2438,7 +2575,7 @@
       <c r="U22" s="6"/>
     </row>
     <row r="23" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A23" s="46"/>
+      <c r="A23" s="80"/>
       <c r="B23" s="2" t="s">
         <v>62</v>
       </c>
@@ -2465,7 +2602,7 @@
       <c r="U23" s="6"/>
     </row>
     <row r="24" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A24" s="46"/>
+      <c r="A24" s="81"/>
       <c r="B24" s="18" t="s">
         <v>63</v>
       </c>
@@ -2492,7 +2629,7 @@
       <c r="U24" s="22"/>
     </row>
     <row r="25" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A25" s="53">
+      <c r="A25" s="72">
         <v>4</v>
       </c>
       <c r="B25" s="13" t="s">
@@ -2541,7 +2678,7 @@
       <c r="U25" s="17"/>
     </row>
     <row r="26" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A26" s="53"/>
+      <c r="A26" s="73"/>
       <c r="B26" s="13" t="s">
         <v>65</v>
       </c>
@@ -2588,7 +2725,7 @@
       <c r="U26" s="17"/>
     </row>
     <row r="27" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A27" s="53"/>
+      <c r="A27" s="73"/>
       <c r="B27" s="13" t="s">
         <v>66</v>
       </c>
@@ -2635,7 +2772,7 @@
       <c r="U27" s="17"/>
     </row>
     <row r="28" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A28" s="53"/>
+      <c r="A28" s="73"/>
       <c r="B28" s="13" t="s">
         <v>67</v>
       </c>
@@ -2682,70 +2819,70 @@
       <c r="U28" s="17"/>
     </row>
     <row r="29" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A29" s="53"/>
+      <c r="A29" s="73"/>
       <c r="B29" s="25" t="s">
         <v>68</v>
       </c>
       <c r="C29" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="D29" s="47" t="s">
+      <c r="D29" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="E29" s="47"/>
-      <c r="F29" s="47"/>
-      <c r="G29" s="47"/>
-      <c r="H29" s="47"/>
-      <c r="I29" s="47"/>
-      <c r="J29" s="47"/>
-      <c r="K29" s="47"/>
-      <c r="L29" s="47"/>
-      <c r="M29" s="47"/>
-      <c r="N29" s="47"/>
-      <c r="O29" s="47"/>
-      <c r="P29" s="47"/>
-      <c r="Q29" s="47"/>
-      <c r="R29" s="47"/>
-      <c r="S29" s="47"/>
-      <c r="T29" s="47"/>
-      <c r="U29" s="48"/>
+      <c r="E29" s="77"/>
+      <c r="F29" s="77"/>
+      <c r="G29" s="77"/>
+      <c r="H29" s="77"/>
+      <c r="I29" s="77"/>
+      <c r="J29" s="77"/>
+      <c r="K29" s="77"/>
+      <c r="L29" s="77"/>
+      <c r="M29" s="77"/>
+      <c r="N29" s="77"/>
+      <c r="O29" s="77"/>
+      <c r="P29" s="77"/>
+      <c r="Q29" s="77"/>
+      <c r="R29" s="77"/>
+      <c r="S29" s="77"/>
+      <c r="T29" s="77"/>
+      <c r="U29" s="50"/>
     </row>
     <row r="30" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A30" s="53"/>
+      <c r="A30" s="73"/>
       <c r="B30" s="25" t="s">
         <v>70</v>
       </c>
       <c r="C30" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="D30" s="49"/>
-      <c r="E30" s="49"/>
-      <c r="F30" s="49"/>
-      <c r="G30" s="49"/>
-      <c r="H30" s="49"/>
-      <c r="I30" s="49"/>
-      <c r="J30" s="49"/>
-      <c r="K30" s="49"/>
-      <c r="L30" s="49"/>
-      <c r="M30" s="49"/>
-      <c r="N30" s="49"/>
-      <c r="O30" s="49"/>
-      <c r="P30" s="49"/>
-      <c r="Q30" s="49"/>
-      <c r="R30" s="49"/>
-      <c r="S30" s="49"/>
-      <c r="T30" s="49"/>
+      <c r="D30" s="76"/>
+      <c r="E30" s="77"/>
+      <c r="F30" s="77"/>
+      <c r="G30" s="77"/>
+      <c r="H30" s="77"/>
+      <c r="I30" s="77"/>
+      <c r="J30" s="77"/>
+      <c r="K30" s="77"/>
+      <c r="L30" s="77"/>
+      <c r="M30" s="77"/>
+      <c r="N30" s="77"/>
+      <c r="O30" s="77"/>
+      <c r="P30" s="77"/>
+      <c r="Q30" s="77"/>
+      <c r="R30" s="77"/>
+      <c r="S30" s="77"/>
+      <c r="T30" s="77"/>
       <c r="U30" s="50"/>
     </row>
     <row r="31" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A31" s="53"/>
+      <c r="A31" s="74"/>
       <c r="B31" s="25" t="s">
         <v>71</v>
       </c>
       <c r="C31" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="D31" s="51"/>
+      <c r="D31" s="78"/>
       <c r="E31" s="51"/>
       <c r="F31" s="51"/>
       <c r="G31" s="51"/>
@@ -2765,7 +2902,7 @@
       <c r="U31" s="52"/>
     </row>
     <row r="32" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A32" s="46">
+      <c r="A32" s="79">
         <v>5</v>
       </c>
       <c r="B32" s="2" t="s">
@@ -2814,7 +2951,7 @@
       <c r="U32" s="6"/>
     </row>
     <row r="33" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A33" s="46"/>
+      <c r="A33" s="80"/>
       <c r="B33" s="2" t="s">
         <v>73</v>
       </c>
@@ -2861,7 +2998,7 @@
       <c r="U33" s="6"/>
     </row>
     <row r="34" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A34" s="46"/>
+      <c r="A34" s="80"/>
       <c r="B34" s="2" t="s">
         <v>74</v>
       </c>
@@ -2908,14 +3045,14 @@
       <c r="U34" s="6"/>
     </row>
     <row r="35" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A35" s="46"/>
+      <c r="A35" s="80"/>
       <c r="B35" s="27" t="s">
         <v>75</v>
       </c>
       <c r="C35" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="D35" s="47" t="s">
+      <c r="D35" s="75" t="s">
         <v>69</v>
       </c>
       <c r="E35" s="47"/>
@@ -2937,88 +3074,88 @@
       <c r="U35" s="48"/>
     </row>
     <row r="36" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A36" s="46"/>
+      <c r="A36" s="80"/>
       <c r="B36" s="27" t="s">
         <v>76</v>
       </c>
       <c r="C36" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="D36" s="49"/>
-      <c r="E36" s="49"/>
-      <c r="F36" s="49"/>
-      <c r="G36" s="49"/>
-      <c r="H36" s="49"/>
-      <c r="I36" s="49"/>
-      <c r="J36" s="49"/>
-      <c r="K36" s="49"/>
-      <c r="L36" s="49"/>
-      <c r="M36" s="49"/>
-      <c r="N36" s="49"/>
-      <c r="O36" s="49"/>
-      <c r="P36" s="49"/>
-      <c r="Q36" s="49"/>
-      <c r="R36" s="49"/>
-      <c r="S36" s="49"/>
-      <c r="T36" s="49"/>
+      <c r="D36" s="76"/>
+      <c r="E36" s="77"/>
+      <c r="F36" s="77"/>
+      <c r="G36" s="77"/>
+      <c r="H36" s="77"/>
+      <c r="I36" s="77"/>
+      <c r="J36" s="77"/>
+      <c r="K36" s="77"/>
+      <c r="L36" s="77"/>
+      <c r="M36" s="77"/>
+      <c r="N36" s="77"/>
+      <c r="O36" s="77"/>
+      <c r="P36" s="77"/>
+      <c r="Q36" s="77"/>
+      <c r="R36" s="77"/>
+      <c r="S36" s="77"/>
+      <c r="T36" s="77"/>
       <c r="U36" s="50"/>
     </row>
     <row r="37" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A37" s="46"/>
+      <c r="A37" s="80"/>
       <c r="B37" s="27" t="s">
         <v>77</v>
       </c>
       <c r="C37" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="D37" s="49"/>
-      <c r="E37" s="49"/>
-      <c r="F37" s="49"/>
-      <c r="G37" s="49"/>
-      <c r="H37" s="49"/>
-      <c r="I37" s="49"/>
-      <c r="J37" s="49"/>
-      <c r="K37" s="49"/>
-      <c r="L37" s="49"/>
-      <c r="M37" s="49"/>
-      <c r="N37" s="49"/>
-      <c r="O37" s="49"/>
-      <c r="P37" s="49"/>
-      <c r="Q37" s="49"/>
-      <c r="R37" s="49"/>
-      <c r="S37" s="49"/>
-      <c r="T37" s="49"/>
+      <c r="D37" s="76"/>
+      <c r="E37" s="77"/>
+      <c r="F37" s="77"/>
+      <c r="G37" s="77"/>
+      <c r="H37" s="77"/>
+      <c r="I37" s="77"/>
+      <c r="J37" s="77"/>
+      <c r="K37" s="77"/>
+      <c r="L37" s="77"/>
+      <c r="M37" s="77"/>
+      <c r="N37" s="77"/>
+      <c r="O37" s="77"/>
+      <c r="P37" s="77"/>
+      <c r="Q37" s="77"/>
+      <c r="R37" s="77"/>
+      <c r="S37" s="77"/>
+      <c r="T37" s="77"/>
       <c r="U37" s="50"/>
     </row>
     <row r="38" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A38" s="46"/>
+      <c r="A38" s="81"/>
       <c r="B38" s="27" t="s">
         <v>78</v>
       </c>
       <c r="C38" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="D38" s="49"/>
-      <c r="E38" s="49"/>
-      <c r="F38" s="49"/>
-      <c r="G38" s="49"/>
-      <c r="H38" s="49"/>
-      <c r="I38" s="49"/>
-      <c r="J38" s="49"/>
-      <c r="K38" s="49"/>
-      <c r="L38" s="49"/>
-      <c r="M38" s="49"/>
-      <c r="N38" s="49"/>
-      <c r="O38" s="49"/>
-      <c r="P38" s="49"/>
-      <c r="Q38" s="49"/>
-      <c r="R38" s="49"/>
-      <c r="S38" s="49"/>
-      <c r="T38" s="49"/>
+      <c r="D38" s="76"/>
+      <c r="E38" s="77"/>
+      <c r="F38" s="77"/>
+      <c r="G38" s="77"/>
+      <c r="H38" s="77"/>
+      <c r="I38" s="77"/>
+      <c r="J38" s="77"/>
+      <c r="K38" s="77"/>
+      <c r="L38" s="77"/>
+      <c r="M38" s="77"/>
+      <c r="N38" s="77"/>
+      <c r="O38" s="77"/>
+      <c r="P38" s="77"/>
+      <c r="Q38" s="77"/>
+      <c r="R38" s="77"/>
+      <c r="S38" s="77"/>
+      <c r="T38" s="77"/>
       <c r="U38" s="50"/>
     </row>
     <row r="39" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A39" s="53">
+      <c r="A39" s="72">
         <v>6</v>
       </c>
       <c r="B39" s="27" t="s">
@@ -3027,61 +3164,61 @@
       <c r="C39" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="49"/>
-      <c r="E39" s="49"/>
-      <c r="F39" s="49"/>
-      <c r="G39" s="49"/>
-      <c r="H39" s="49"/>
-      <c r="I39" s="49"/>
-      <c r="J39" s="49"/>
-      <c r="K39" s="49"/>
-      <c r="L39" s="49"/>
-      <c r="M39" s="49"/>
-      <c r="N39" s="49"/>
-      <c r="O39" s="49"/>
-      <c r="P39" s="49"/>
-      <c r="Q39" s="49"/>
-      <c r="R39" s="49"/>
-      <c r="S39" s="49"/>
-      <c r="T39" s="49"/>
+      <c r="D39" s="76"/>
+      <c r="E39" s="77"/>
+      <c r="F39" s="77"/>
+      <c r="G39" s="77"/>
+      <c r="H39" s="77"/>
+      <c r="I39" s="77"/>
+      <c r="J39" s="77"/>
+      <c r="K39" s="77"/>
+      <c r="L39" s="77"/>
+      <c r="M39" s="77"/>
+      <c r="N39" s="77"/>
+      <c r="O39" s="77"/>
+      <c r="P39" s="77"/>
+      <c r="Q39" s="77"/>
+      <c r="R39" s="77"/>
+      <c r="S39" s="77"/>
+      <c r="T39" s="77"/>
       <c r="U39" s="50"/>
     </row>
     <row r="40" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A40" s="53"/>
+      <c r="A40" s="73"/>
       <c r="B40" s="27" t="s">
         <v>80</v>
       </c>
       <c r="C40" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="D40" s="49"/>
-      <c r="E40" s="49"/>
-      <c r="F40" s="49"/>
-      <c r="G40" s="49"/>
-      <c r="H40" s="49"/>
-      <c r="I40" s="49"/>
-      <c r="J40" s="49"/>
-      <c r="K40" s="49"/>
-      <c r="L40" s="49"/>
-      <c r="M40" s="49"/>
-      <c r="N40" s="49"/>
-      <c r="O40" s="49"/>
-      <c r="P40" s="49"/>
-      <c r="Q40" s="49"/>
-      <c r="R40" s="49"/>
-      <c r="S40" s="49"/>
-      <c r="T40" s="49"/>
+      <c r="D40" s="76"/>
+      <c r="E40" s="77"/>
+      <c r="F40" s="77"/>
+      <c r="G40" s="77"/>
+      <c r="H40" s="77"/>
+      <c r="I40" s="77"/>
+      <c r="J40" s="77"/>
+      <c r="K40" s="77"/>
+      <c r="L40" s="77"/>
+      <c r="M40" s="77"/>
+      <c r="N40" s="77"/>
+      <c r="O40" s="77"/>
+      <c r="P40" s="77"/>
+      <c r="Q40" s="77"/>
+      <c r="R40" s="77"/>
+      <c r="S40" s="77"/>
+      <c r="T40" s="77"/>
       <c r="U40" s="50"/>
     </row>
     <row r="41" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A41" s="53"/>
+      <c r="A41" s="73"/>
       <c r="B41" s="27" t="s">
         <v>81</v>
       </c>
       <c r="C41" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="D41" s="51"/>
+      <c r="D41" s="78"/>
       <c r="E41" s="51"/>
       <c r="F41" s="51"/>
       <c r="G41" s="51"/>
@@ -3101,7 +3238,7 @@
       <c r="U41" s="52"/>
     </row>
     <row r="42" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A42" s="53"/>
+      <c r="A42" s="73"/>
       <c r="B42" s="28" t="s">
         <v>82</v>
       </c>
@@ -3160,7 +3297,7 @@
       </c>
     </row>
     <row r="43" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A43" s="53"/>
+      <c r="A43" s="73"/>
       <c r="B43" s="28" t="s">
         <v>83</v>
       </c>
@@ -3189,7 +3326,7 @@
       <c r="U43" s="17"/>
     </row>
     <row r="44" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A44" s="53"/>
+      <c r="A44" s="73"/>
       <c r="B44" s="29" t="s">
         <v>84</v>
       </c>
@@ -3216,7 +3353,7 @@
       <c r="U44" s="22"/>
     </row>
     <row r="45" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A45" s="53"/>
+      <c r="A45" s="74"/>
       <c r="B45" s="28" t="s">
         <v>85</v>
       </c>
@@ -3243,7 +3380,7 @@
       <c r="U45" s="17"/>
     </row>
     <row r="46" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A46" s="46">
+      <c r="A46" s="79">
         <v>7</v>
       </c>
       <c r="B46" s="30" t="s">
@@ -3292,7 +3429,7 @@
       <c r="U46" s="6"/>
     </row>
     <row r="47" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A47" s="46"/>
+      <c r="A47" s="80"/>
       <c r="B47" s="30" t="s">
         <v>87</v>
       </c>
@@ -3339,7 +3476,7 @@
       <c r="U47" s="6"/>
     </row>
     <row r="48" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A48" s="46"/>
+      <c r="A48" s="80"/>
       <c r="B48" s="30" t="s">
         <v>88</v>
       </c>
@@ -3386,7 +3523,7 @@
       <c r="U48" s="6"/>
     </row>
     <row r="49" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A49" s="46"/>
+      <c r="A49" s="80"/>
       <c r="B49" s="30" t="s">
         <v>89</v>
       </c>
@@ -3433,7 +3570,7 @@
       <c r="U49" s="6"/>
     </row>
     <row r="50" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A50" s="46"/>
+      <c r="A50" s="80"/>
       <c r="B50" s="30" t="s">
         <v>90</v>
       </c>
@@ -3480,7 +3617,7 @@
       <c r="U50" s="6"/>
     </row>
     <row r="51" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A51" s="46"/>
+      <c r="A51" s="80"/>
       <c r="B51" s="30" t="s">
         <v>91</v>
       </c>
@@ -3507,7 +3644,7 @@
       <c r="U51" s="6"/>
     </row>
     <row r="52" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A52" s="46"/>
+      <c r="A52" s="81"/>
       <c r="B52" s="30" t="s">
         <v>92</v>
       </c>
@@ -3534,7 +3671,7 @@
       <c r="U52" s="6"/>
     </row>
     <row r="53" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A53" s="53">
+      <c r="A53" s="72">
         <v>8</v>
       </c>
       <c r="B53" s="28" t="s">
@@ -3583,7 +3720,7 @@
       <c r="U53" s="17"/>
     </row>
     <row r="54" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A54" s="53"/>
+      <c r="A54" s="73"/>
       <c r="B54" s="28" t="s">
         <v>94</v>
       </c>
@@ -3630,7 +3767,7 @@
       <c r="U54" s="17"/>
     </row>
     <row r="55" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A55" s="53"/>
+      <c r="A55" s="73"/>
       <c r="B55" s="28" t="s">
         <v>95</v>
       </c>
@@ -3677,7 +3814,7 @@
       <c r="U55" s="17"/>
     </row>
     <row r="56" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A56" s="53"/>
+      <c r="A56" s="73"/>
       <c r="B56" s="28" t="s">
         <v>96</v>
       </c>
@@ -3736,7 +3873,7 @@
       </c>
     </row>
     <row r="57" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A57" s="53"/>
+      <c r="A57" s="73"/>
       <c r="B57" s="28" t="s">
         <v>97</v>
       </c>
@@ -3783,7 +3920,7 @@
       <c r="U57" s="17"/>
     </row>
     <row r="58" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A58" s="53"/>
+      <c r="A58" s="73"/>
       <c r="B58" s="28" t="s">
         <v>98</v>
       </c>
@@ -3810,7 +3947,7 @@
       <c r="U58" s="17"/>
     </row>
     <row r="59" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A59" s="53"/>
+      <c r="A59" s="74"/>
       <c r="B59" s="28" t="s">
         <v>99</v>
       </c>
@@ -3837,7 +3974,7 @@
       <c r="U59" s="17"/>
     </row>
     <row r="60" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A60" s="46">
+      <c r="A60" s="79">
         <v>9</v>
       </c>
       <c r="B60" s="30" t="s">
@@ -3886,7 +4023,7 @@
       <c r="U60" s="6"/>
     </row>
     <row r="61" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A61" s="46"/>
+      <c r="A61" s="80"/>
       <c r="B61" s="30" t="s">
         <v>101</v>
       </c>
@@ -3915,7 +4052,7 @@
       <c r="U61" s="6"/>
     </row>
     <row r="62" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A62" s="46"/>
+      <c r="A62" s="80"/>
       <c r="B62" s="30" t="s">
         <v>102</v>
       </c>
@@ -3962,7 +4099,7 @@
       <c r="U62" s="6"/>
     </row>
     <row r="63" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A63" s="46"/>
+      <c r="A63" s="80"/>
       <c r="B63" s="30" t="s">
         <v>103</v>
       </c>
@@ -4021,7 +4158,7 @@
       </c>
     </row>
     <row r="64" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A64" s="46"/>
+      <c r="A64" s="80"/>
       <c r="B64" s="30" t="s">
         <v>104</v>
       </c>
@@ -4050,7 +4187,7 @@
       <c r="U64" s="5"/>
     </row>
     <row r="65" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A65" s="46"/>
+      <c r="A65" s="80"/>
       <c r="B65" s="30" t="s">
         <v>105</v>
       </c>
@@ -4077,7 +4214,7 @@
       <c r="U65" s="5"/>
     </row>
     <row r="66" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A66" s="46"/>
+      <c r="A66" s="81"/>
       <c r="B66" s="30" t="s">
         <v>106</v>
       </c>
@@ -4104,7 +4241,7 @@
       <c r="U66" s="5"/>
     </row>
     <row r="67" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A67" s="53">
+      <c r="A67" s="72">
         <v>10</v>
       </c>
       <c r="B67" s="28" t="s">
@@ -4153,7 +4290,7 @@
       <c r="U67" s="16"/>
     </row>
     <row r="68" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A68" s="53"/>
+      <c r="A68" s="73"/>
       <c r="B68" s="28" t="s">
         <v>108</v>
       </c>
@@ -4182,7 +4319,7 @@
       <c r="U68" s="16"/>
     </row>
     <row r="69" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A69" s="53"/>
+      <c r="A69" s="73"/>
       <c r="B69" s="28" t="s">
         <v>109</v>
       </c>
@@ -4211,7 +4348,7 @@
       <c r="U69" s="16"/>
     </row>
     <row r="70" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A70" s="53"/>
+      <c r="A70" s="73"/>
       <c r="B70" s="28" t="s">
         <v>110</v>
       </c>
@@ -4270,7 +4407,7 @@
       </c>
     </row>
     <row r="71" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A71" s="53"/>
+      <c r="A71" s="73"/>
       <c r="B71" s="28" t="s">
         <v>111</v>
       </c>
@@ -4299,7 +4436,7 @@
       <c r="U71" s="16"/>
     </row>
     <row r="72" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A72" s="53"/>
+      <c r="A72" s="73"/>
       <c r="B72" s="28" t="s">
         <v>112</v>
       </c>
@@ -4326,7 +4463,7 @@
       <c r="U72" s="16"/>
     </row>
     <row r="73" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A73" s="53"/>
+      <c r="A73" s="74"/>
       <c r="B73" s="28" t="s">
         <v>113</v>
       </c>
@@ -4353,7 +4490,7 @@
       <c r="U73" s="16"/>
     </row>
     <row r="74" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A74" s="46">
+      <c r="A74" s="79">
         <v>11</v>
       </c>
       <c r="B74" s="30" t="s">
@@ -4402,7 +4539,7 @@
       <c r="U74" s="5"/>
     </row>
     <row r="75" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A75" s="46"/>
+      <c r="A75" s="80"/>
       <c r="B75" s="30" t="s">
         <v>115</v>
       </c>
@@ -4431,7 +4568,7 @@
       <c r="U75" s="5"/>
     </row>
     <row r="76" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A76" s="46"/>
+      <c r="A76" s="80"/>
       <c r="B76" s="30" t="s">
         <v>116</v>
       </c>
@@ -4460,7 +4597,7 @@
       <c r="U76" s="5"/>
     </row>
     <row r="77" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A77" s="46"/>
+      <c r="A77" s="80"/>
       <c r="B77" s="30" t="s">
         <v>117</v>
       </c>
@@ -4507,7 +4644,7 @@
       <c r="U77" s="6"/>
     </row>
     <row r="78" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A78" s="46"/>
+      <c r="A78" s="80"/>
       <c r="B78" s="30" t="s">
         <v>118</v>
       </c>
@@ -4536,7 +4673,7 @@
       <c r="U78" s="6"/>
     </row>
     <row r="79" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A79" s="46"/>
+      <c r="A79" s="80"/>
       <c r="B79" s="30" t="s">
         <v>119</v>
       </c>
@@ -4563,7 +4700,7 @@
       <c r="U79" s="6"/>
     </row>
     <row r="80" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A80" s="46"/>
+      <c r="A80" s="81"/>
       <c r="B80" s="30" t="s">
         <v>120</v>
       </c>
@@ -4590,7 +4727,7 @@
       <c r="U80" s="6"/>
     </row>
     <row r="81" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A81" s="53">
+      <c r="A81" s="72">
         <v>12</v>
       </c>
       <c r="B81" s="28" t="s">
@@ -4599,7 +4736,7 @@
       <c r="C81" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="D81" s="61" t="s">
+      <c r="D81" s="82" t="s">
         <v>122</v>
       </c>
       <c r="E81" s="61"/>
@@ -4621,169 +4758,169 @@
       <c r="U81" s="62"/>
     </row>
     <row r="82" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A82" s="53"/>
+      <c r="A82" s="73"/>
       <c r="B82" s="28" t="s">
         <v>123</v>
       </c>
       <c r="C82" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D82" s="63"/>
-      <c r="E82" s="63"/>
-      <c r="F82" s="63"/>
-      <c r="G82" s="63"/>
-      <c r="H82" s="63"/>
-      <c r="I82" s="63"/>
-      <c r="J82" s="63"/>
-      <c r="K82" s="63"/>
-      <c r="L82" s="63"/>
-      <c r="M82" s="63"/>
-      <c r="N82" s="63"/>
-      <c r="O82" s="63"/>
-      <c r="P82" s="63"/>
-      <c r="Q82" s="63"/>
-      <c r="R82" s="63"/>
-      <c r="S82" s="63"/>
-      <c r="T82" s="63"/>
+      <c r="D82" s="83"/>
+      <c r="E82" s="84"/>
+      <c r="F82" s="84"/>
+      <c r="G82" s="84"/>
+      <c r="H82" s="84"/>
+      <c r="I82" s="84"/>
+      <c r="J82" s="84"/>
+      <c r="K82" s="84"/>
+      <c r="L82" s="84"/>
+      <c r="M82" s="84"/>
+      <c r="N82" s="84"/>
+      <c r="O82" s="84"/>
+      <c r="P82" s="84"/>
+      <c r="Q82" s="84"/>
+      <c r="R82" s="84"/>
+      <c r="S82" s="84"/>
+      <c r="T82" s="84"/>
       <c r="U82" s="64"/>
     </row>
     <row r="83" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A83" s="53"/>
+      <c r="A83" s="73"/>
       <c r="B83" s="28" t="s">
         <v>124</v>
       </c>
       <c r="C83" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="D83" s="63"/>
-      <c r="E83" s="63"/>
-      <c r="F83" s="63"/>
-      <c r="G83" s="63"/>
-      <c r="H83" s="63"/>
-      <c r="I83" s="63"/>
-      <c r="J83" s="63"/>
-      <c r="K83" s="63"/>
-      <c r="L83" s="63"/>
-      <c r="M83" s="63"/>
-      <c r="N83" s="63"/>
-      <c r="O83" s="63"/>
-      <c r="P83" s="63"/>
-      <c r="Q83" s="63"/>
-      <c r="R83" s="63"/>
-      <c r="S83" s="63"/>
-      <c r="T83" s="63"/>
+      <c r="D83" s="83"/>
+      <c r="E83" s="84"/>
+      <c r="F83" s="84"/>
+      <c r="G83" s="84"/>
+      <c r="H83" s="84"/>
+      <c r="I83" s="84"/>
+      <c r="J83" s="84"/>
+      <c r="K83" s="84"/>
+      <c r="L83" s="84"/>
+      <c r="M83" s="84"/>
+      <c r="N83" s="84"/>
+      <c r="O83" s="84"/>
+      <c r="P83" s="84"/>
+      <c r="Q83" s="84"/>
+      <c r="R83" s="84"/>
+      <c r="S83" s="84"/>
+      <c r="T83" s="84"/>
       <c r="U83" s="64"/>
     </row>
     <row r="84" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A84" s="53"/>
+      <c r="A84" s="73"/>
       <c r="B84" s="28" t="s">
         <v>125</v>
       </c>
       <c r="C84" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="D84" s="63"/>
-      <c r="E84" s="63"/>
-      <c r="F84" s="63"/>
-      <c r="G84" s="63"/>
-      <c r="H84" s="63"/>
-      <c r="I84" s="63"/>
-      <c r="J84" s="63"/>
-      <c r="K84" s="63"/>
-      <c r="L84" s="63"/>
-      <c r="M84" s="63"/>
-      <c r="N84" s="63"/>
-      <c r="O84" s="63"/>
-      <c r="P84" s="63"/>
-      <c r="Q84" s="63"/>
-      <c r="R84" s="63"/>
-      <c r="S84" s="63"/>
-      <c r="T84" s="63"/>
+      <c r="D84" s="83"/>
+      <c r="E84" s="84"/>
+      <c r="F84" s="84"/>
+      <c r="G84" s="84"/>
+      <c r="H84" s="84"/>
+      <c r="I84" s="84"/>
+      <c r="J84" s="84"/>
+      <c r="K84" s="84"/>
+      <c r="L84" s="84"/>
+      <c r="M84" s="84"/>
+      <c r="N84" s="84"/>
+      <c r="O84" s="84"/>
+      <c r="P84" s="84"/>
+      <c r="Q84" s="84"/>
+      <c r="R84" s="84"/>
+      <c r="S84" s="84"/>
+      <c r="T84" s="84"/>
       <c r="U84" s="64"/>
     </row>
     <row r="85" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A85" s="53"/>
+      <c r="A85" s="73"/>
       <c r="B85" s="28" t="s">
         <v>126</v>
       </c>
       <c r="C85" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="D85" s="63"/>
-      <c r="E85" s="63"/>
-      <c r="F85" s="63"/>
-      <c r="G85" s="63"/>
-      <c r="H85" s="63"/>
-      <c r="I85" s="63"/>
-      <c r="J85" s="63"/>
-      <c r="K85" s="63"/>
-      <c r="L85" s="63"/>
-      <c r="M85" s="63"/>
-      <c r="N85" s="63"/>
-      <c r="O85" s="63"/>
-      <c r="P85" s="63"/>
-      <c r="Q85" s="63"/>
-      <c r="R85" s="63"/>
-      <c r="S85" s="63"/>
-      <c r="T85" s="63"/>
+      <c r="D85" s="83"/>
+      <c r="E85" s="84"/>
+      <c r="F85" s="84"/>
+      <c r="G85" s="84"/>
+      <c r="H85" s="84"/>
+      <c r="I85" s="84"/>
+      <c r="J85" s="84"/>
+      <c r="K85" s="84"/>
+      <c r="L85" s="84"/>
+      <c r="M85" s="84"/>
+      <c r="N85" s="84"/>
+      <c r="O85" s="84"/>
+      <c r="P85" s="84"/>
+      <c r="Q85" s="84"/>
+      <c r="R85" s="84"/>
+      <c r="S85" s="84"/>
+      <c r="T85" s="84"/>
       <c r="U85" s="64"/>
     </row>
     <row r="86" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A86" s="53"/>
+      <c r="A86" s="73"/>
       <c r="B86" s="28" t="s">
         <v>127</v>
       </c>
       <c r="C86" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="D86" s="63"/>
-      <c r="E86" s="63"/>
-      <c r="F86" s="63"/>
-      <c r="G86" s="63"/>
-      <c r="H86" s="63"/>
-      <c r="I86" s="63"/>
-      <c r="J86" s="63"/>
-      <c r="K86" s="63"/>
-      <c r="L86" s="63"/>
-      <c r="M86" s="63"/>
-      <c r="N86" s="63"/>
-      <c r="O86" s="63"/>
-      <c r="P86" s="63"/>
-      <c r="Q86" s="63"/>
-      <c r="R86" s="63"/>
-      <c r="S86" s="63"/>
-      <c r="T86" s="63"/>
+      <c r="D86" s="83"/>
+      <c r="E86" s="84"/>
+      <c r="F86" s="84"/>
+      <c r="G86" s="84"/>
+      <c r="H86" s="84"/>
+      <c r="I86" s="84"/>
+      <c r="J86" s="84"/>
+      <c r="K86" s="84"/>
+      <c r="L86" s="84"/>
+      <c r="M86" s="84"/>
+      <c r="N86" s="84"/>
+      <c r="O86" s="84"/>
+      <c r="P86" s="84"/>
+      <c r="Q86" s="84"/>
+      <c r="R86" s="84"/>
+      <c r="S86" s="84"/>
+      <c r="T86" s="84"/>
       <c r="U86" s="64"/>
     </row>
     <row r="87" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A87" s="53"/>
+      <c r="A87" s="74"/>
       <c r="B87" s="28" t="s">
         <v>128</v>
       </c>
       <c r="C87" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="D87" s="63"/>
-      <c r="E87" s="63"/>
-      <c r="F87" s="63"/>
-      <c r="G87" s="63"/>
-      <c r="H87" s="63"/>
-      <c r="I87" s="63"/>
-      <c r="J87" s="63"/>
-      <c r="K87" s="63"/>
-      <c r="L87" s="63"/>
-      <c r="M87" s="63"/>
-      <c r="N87" s="63"/>
-      <c r="O87" s="63"/>
-      <c r="P87" s="63"/>
-      <c r="Q87" s="63"/>
-      <c r="R87" s="63"/>
-      <c r="S87" s="63"/>
-      <c r="T87" s="63"/>
+      <c r="D87" s="83"/>
+      <c r="E87" s="84"/>
+      <c r="F87" s="84"/>
+      <c r="G87" s="84"/>
+      <c r="H87" s="84"/>
+      <c r="I87" s="84"/>
+      <c r="J87" s="84"/>
+      <c r="K87" s="84"/>
+      <c r="L87" s="84"/>
+      <c r="M87" s="84"/>
+      <c r="N87" s="84"/>
+      <c r="O87" s="84"/>
+      <c r="P87" s="84"/>
+      <c r="Q87" s="84"/>
+      <c r="R87" s="84"/>
+      <c r="S87" s="84"/>
+      <c r="T87" s="84"/>
       <c r="U87" s="64"/>
     </row>
     <row r="88" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A88" s="46">
+      <c r="A88" s="79">
         <v>13</v>
       </c>
       <c r="B88" s="30" t="s">
@@ -4792,169 +4929,169 @@
       <c r="C88" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D88" s="63"/>
-      <c r="E88" s="63"/>
-      <c r="F88" s="63"/>
-      <c r="G88" s="63"/>
-      <c r="H88" s="63"/>
-      <c r="I88" s="63"/>
-      <c r="J88" s="63"/>
-      <c r="K88" s="63"/>
-      <c r="L88" s="63"/>
-      <c r="M88" s="63"/>
-      <c r="N88" s="63"/>
-      <c r="O88" s="63"/>
-      <c r="P88" s="63"/>
-      <c r="Q88" s="63"/>
-      <c r="R88" s="63"/>
-      <c r="S88" s="63"/>
-      <c r="T88" s="63"/>
+      <c r="D88" s="83"/>
+      <c r="E88" s="84"/>
+      <c r="F88" s="84"/>
+      <c r="G88" s="84"/>
+      <c r="H88" s="84"/>
+      <c r="I88" s="84"/>
+      <c r="J88" s="84"/>
+      <c r="K88" s="84"/>
+      <c r="L88" s="84"/>
+      <c r="M88" s="84"/>
+      <c r="N88" s="84"/>
+      <c r="O88" s="84"/>
+      <c r="P88" s="84"/>
+      <c r="Q88" s="84"/>
+      <c r="R88" s="84"/>
+      <c r="S88" s="84"/>
+      <c r="T88" s="84"/>
       <c r="U88" s="64"/>
     </row>
     <row r="89" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A89" s="46"/>
+      <c r="A89" s="80"/>
       <c r="B89" s="30" t="s">
         <v>130</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D89" s="63"/>
-      <c r="E89" s="63"/>
-      <c r="F89" s="63"/>
-      <c r="G89" s="63"/>
-      <c r="H89" s="63"/>
-      <c r="I89" s="63"/>
-      <c r="J89" s="63"/>
-      <c r="K89" s="63"/>
-      <c r="L89" s="63"/>
-      <c r="M89" s="63"/>
-      <c r="N89" s="63"/>
-      <c r="O89" s="63"/>
-      <c r="P89" s="63"/>
-      <c r="Q89" s="63"/>
-      <c r="R89" s="63"/>
-      <c r="S89" s="63"/>
-      <c r="T89" s="63"/>
+      <c r="D89" s="83"/>
+      <c r="E89" s="84"/>
+      <c r="F89" s="84"/>
+      <c r="G89" s="84"/>
+      <c r="H89" s="84"/>
+      <c r="I89" s="84"/>
+      <c r="J89" s="84"/>
+      <c r="K89" s="84"/>
+      <c r="L89" s="84"/>
+      <c r="M89" s="84"/>
+      <c r="N89" s="84"/>
+      <c r="O89" s="84"/>
+      <c r="P89" s="84"/>
+      <c r="Q89" s="84"/>
+      <c r="R89" s="84"/>
+      <c r="S89" s="84"/>
+      <c r="T89" s="84"/>
       <c r="U89" s="64"/>
     </row>
     <row r="90" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A90" s="46"/>
+      <c r="A90" s="80"/>
       <c r="B90" s="30" t="s">
         <v>131</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D90" s="63"/>
-      <c r="E90" s="63"/>
-      <c r="F90" s="63"/>
-      <c r="G90" s="63"/>
-      <c r="H90" s="63"/>
-      <c r="I90" s="63"/>
-      <c r="J90" s="63"/>
-      <c r="K90" s="63"/>
-      <c r="L90" s="63"/>
-      <c r="M90" s="63"/>
-      <c r="N90" s="63"/>
-      <c r="O90" s="63"/>
-      <c r="P90" s="63"/>
-      <c r="Q90" s="63"/>
-      <c r="R90" s="63"/>
-      <c r="S90" s="63"/>
-      <c r="T90" s="63"/>
+      <c r="D90" s="83"/>
+      <c r="E90" s="84"/>
+      <c r="F90" s="84"/>
+      <c r="G90" s="84"/>
+      <c r="H90" s="84"/>
+      <c r="I90" s="84"/>
+      <c r="J90" s="84"/>
+      <c r="K90" s="84"/>
+      <c r="L90" s="84"/>
+      <c r="M90" s="84"/>
+      <c r="N90" s="84"/>
+      <c r="O90" s="84"/>
+      <c r="P90" s="84"/>
+      <c r="Q90" s="84"/>
+      <c r="R90" s="84"/>
+      <c r="S90" s="84"/>
+      <c r="T90" s="84"/>
       <c r="U90" s="64"/>
     </row>
     <row r="91" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A91" s="46"/>
+      <c r="A91" s="80"/>
       <c r="B91" s="30" t="s">
         <v>132</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D91" s="63"/>
-      <c r="E91" s="63"/>
-      <c r="F91" s="63"/>
-      <c r="G91" s="63"/>
-      <c r="H91" s="63"/>
-      <c r="I91" s="63"/>
-      <c r="J91" s="63"/>
-      <c r="K91" s="63"/>
-      <c r="L91" s="63"/>
-      <c r="M91" s="63"/>
-      <c r="N91" s="63"/>
-      <c r="O91" s="63"/>
-      <c r="P91" s="63"/>
-      <c r="Q91" s="63"/>
-      <c r="R91" s="63"/>
-      <c r="S91" s="63"/>
-      <c r="T91" s="63"/>
+      <c r="D91" s="83"/>
+      <c r="E91" s="84"/>
+      <c r="F91" s="84"/>
+      <c r="G91" s="84"/>
+      <c r="H91" s="84"/>
+      <c r="I91" s="84"/>
+      <c r="J91" s="84"/>
+      <c r="K91" s="84"/>
+      <c r="L91" s="84"/>
+      <c r="M91" s="84"/>
+      <c r="N91" s="84"/>
+      <c r="O91" s="84"/>
+      <c r="P91" s="84"/>
+      <c r="Q91" s="84"/>
+      <c r="R91" s="84"/>
+      <c r="S91" s="84"/>
+      <c r="T91" s="84"/>
       <c r="U91" s="64"/>
     </row>
     <row r="92" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A92" s="46"/>
+      <c r="A92" s="80"/>
       <c r="B92" s="30" t="s">
         <v>133</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D92" s="63"/>
-      <c r="E92" s="63"/>
-      <c r="F92" s="63"/>
-      <c r="G92" s="63"/>
-      <c r="H92" s="63"/>
-      <c r="I92" s="63"/>
-      <c r="J92" s="63"/>
-      <c r="K92" s="63"/>
-      <c r="L92" s="63"/>
-      <c r="M92" s="63"/>
-      <c r="N92" s="63"/>
-      <c r="O92" s="63"/>
-      <c r="P92" s="63"/>
-      <c r="Q92" s="63"/>
-      <c r="R92" s="63"/>
-      <c r="S92" s="63"/>
-      <c r="T92" s="63"/>
+      <c r="D92" s="83"/>
+      <c r="E92" s="84"/>
+      <c r="F92" s="84"/>
+      <c r="G92" s="84"/>
+      <c r="H92" s="84"/>
+      <c r="I92" s="84"/>
+      <c r="J92" s="84"/>
+      <c r="K92" s="84"/>
+      <c r="L92" s="84"/>
+      <c r="M92" s="84"/>
+      <c r="N92" s="84"/>
+      <c r="O92" s="84"/>
+      <c r="P92" s="84"/>
+      <c r="Q92" s="84"/>
+      <c r="R92" s="84"/>
+      <c r="S92" s="84"/>
+      <c r="T92" s="84"/>
       <c r="U92" s="64"/>
     </row>
     <row r="93" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A93" s="46"/>
+      <c r="A93" s="80"/>
       <c r="B93" s="30" t="s">
         <v>134</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D93" s="63"/>
-      <c r="E93" s="63"/>
-      <c r="F93" s="63"/>
-      <c r="G93" s="63"/>
-      <c r="H93" s="63"/>
-      <c r="I93" s="63"/>
-      <c r="J93" s="63"/>
-      <c r="K93" s="63"/>
-      <c r="L93" s="63"/>
-      <c r="M93" s="63"/>
-      <c r="N93" s="63"/>
-      <c r="O93" s="63"/>
-      <c r="P93" s="63"/>
-      <c r="Q93" s="63"/>
-      <c r="R93" s="63"/>
-      <c r="S93" s="63"/>
-      <c r="T93" s="63"/>
+      <c r="D93" s="83"/>
+      <c r="E93" s="84"/>
+      <c r="F93" s="84"/>
+      <c r="G93" s="84"/>
+      <c r="H93" s="84"/>
+      <c r="I93" s="84"/>
+      <c r="J93" s="84"/>
+      <c r="K93" s="84"/>
+      <c r="L93" s="84"/>
+      <c r="M93" s="84"/>
+      <c r="N93" s="84"/>
+      <c r="O93" s="84"/>
+      <c r="P93" s="84"/>
+      <c r="Q93" s="84"/>
+      <c r="R93" s="84"/>
+      <c r="S93" s="84"/>
+      <c r="T93" s="84"/>
       <c r="U93" s="64"/>
     </row>
     <row r="94" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A94" s="46"/>
+      <c r="A94" s="81"/>
       <c r="B94" s="30" t="s">
         <v>135</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D94" s="65"/>
+      <c r="D94" s="85"/>
       <c r="E94" s="65"/>
       <c r="F94" s="65"/>
       <c r="G94" s="65"/>
@@ -4974,7 +5111,7 @@
       <c r="U94" s="66"/>
     </row>
     <row r="95" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A95" s="53">
+      <c r="A95" s="72">
         <v>14</v>
       </c>
       <c r="B95" s="28" t="s">
@@ -5007,7 +5144,7 @@
       <c r="U95" s="17"/>
     </row>
     <row r="96" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A96" s="53"/>
+      <c r="A96" s="73"/>
       <c r="B96" s="28" t="s">
         <v>138</v>
       </c>
@@ -5038,7 +5175,7 @@
       <c r="U96" s="17"/>
     </row>
     <row r="97" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A97" s="53"/>
+      <c r="A97" s="73"/>
       <c r="B97" s="28" t="s">
         <v>139</v>
       </c>
@@ -5069,7 +5206,7 @@
       <c r="U97" s="17"/>
     </row>
     <row r="98" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A98" s="53"/>
+      <c r="A98" s="73"/>
       <c r="B98" s="28" t="s">
         <v>140</v>
       </c>
@@ -5100,7 +5237,7 @@
       <c r="U98" s="17"/>
     </row>
     <row r="99" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A99" s="53"/>
+      <c r="A99" s="73"/>
       <c r="B99" s="28" t="s">
         <v>141</v>
       </c>
@@ -5131,7 +5268,7 @@
       <c r="U99" s="17"/>
     </row>
     <row r="100" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A100" s="53"/>
+      <c r="A100" s="73"/>
       <c r="B100" s="28" t="s">
         <v>142</v>
       </c>
@@ -5162,7 +5299,7 @@
       <c r="U100" s="17"/>
     </row>
     <row r="101" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A101" s="53"/>
+      <c r="A101" s="74"/>
       <c r="B101" s="28" t="s">
         <v>143</v>
       </c>
@@ -5193,7 +5330,7 @@
       <c r="U101" s="17"/>
     </row>
     <row r="102" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A102" s="46">
+      <c r="A102" s="79">
         <v>15</v>
       </c>
       <c r="B102" s="30" t="s">
@@ -5226,7 +5363,7 @@
       <c r="U102" s="6"/>
     </row>
     <row r="103" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A103" s="46"/>
+      <c r="A103" s="80"/>
       <c r="B103" s="30" t="s">
         <v>145</v>
       </c>
@@ -5257,7 +5394,7 @@
       <c r="U103" s="6"/>
     </row>
     <row r="104" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A104" s="46"/>
+      <c r="A104" s="80"/>
       <c r="B104" s="30" t="s">
         <v>146</v>
       </c>
@@ -5288,7 +5425,7 @@
       <c r="U104" s="6"/>
     </row>
     <row r="105" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A105" s="46"/>
+      <c r="A105" s="80"/>
       <c r="B105" s="30" t="s">
         <v>147</v>
       </c>
@@ -5319,7 +5456,7 @@
       <c r="U105" s="6"/>
     </row>
     <row r="106" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A106" s="46"/>
+      <c r="A106" s="80"/>
       <c r="B106" s="30" t="s">
         <v>148</v>
       </c>
@@ -5350,7 +5487,7 @@
       <c r="U106" s="6"/>
     </row>
     <row r="107" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A107" s="46"/>
+      <c r="A107" s="80"/>
       <c r="B107" s="30" t="s">
         <v>149</v>
       </c>
@@ -5381,7 +5518,7 @@
       <c r="U107" s="6"/>
     </row>
     <row r="108" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A108" s="46"/>
+      <c r="A108" s="81"/>
       <c r="B108" s="30" t="s">
         <v>150</v>
       </c>
@@ -5412,7 +5549,7 @@
       <c r="U108" s="6"/>
     </row>
     <row r="109" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A109" s="53">
+      <c r="A109" s="72">
         <v>16</v>
       </c>
       <c r="B109" s="28" t="s">
@@ -5445,7 +5582,7 @@
       <c r="U109" s="16"/>
     </row>
     <row r="110" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A110" s="53"/>
+      <c r="A110" s="73"/>
       <c r="B110" s="28" t="s">
         <v>152</v>
       </c>
@@ -5476,7 +5613,7 @@
       <c r="U110" s="16"/>
     </row>
     <row r="111" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A111" s="53"/>
+      <c r="A111" s="73"/>
       <c r="B111" s="28" t="s">
         <v>153</v>
       </c>
@@ -5507,7 +5644,7 @@
       <c r="U111" s="16"/>
     </row>
     <row r="112" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A112" s="53"/>
+      <c r="A112" s="73"/>
       <c r="B112" s="28" t="s">
         <v>154</v>
       </c>
@@ -5538,7 +5675,7 @@
       <c r="U112" s="16"/>
     </row>
     <row r="113" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A113" s="53"/>
+      <c r="A113" s="73"/>
       <c r="B113" s="28" t="s">
         <v>155</v>
       </c>
@@ -5569,7 +5706,7 @@
       <c r="U113" s="16"/>
     </row>
     <row r="114" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A114" s="53"/>
+      <c r="A114" s="73"/>
       <c r="B114" s="28" t="s">
         <v>156</v>
       </c>
@@ -5600,7 +5737,7 @@
       <c r="U114" s="16"/>
     </row>
     <row r="115" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A115" s="53"/>
+      <c r="A115" s="74"/>
       <c r="B115" s="28" t="s">
         <v>157</v>
       </c>
@@ -5631,7 +5768,7 @@
       <c r="U115" s="16"/>
     </row>
     <row r="116" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A116" s="46">
+      <c r="A116" s="79">
         <v>17</v>
       </c>
       <c r="B116" s="30" t="s">
@@ -5664,7 +5801,7 @@
       <c r="U116" s="6"/>
     </row>
     <row r="117" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A117" s="46"/>
+      <c r="A117" s="80"/>
       <c r="B117" s="30" t="s">
         <v>159</v>
       </c>
@@ -5695,7 +5832,7 @@
       <c r="U117" s="6"/>
     </row>
     <row r="118" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A118" s="46"/>
+      <c r="A118" s="80"/>
       <c r="B118" s="30" t="s">
         <v>160</v>
       </c>
@@ -5726,7 +5863,7 @@
       <c r="U118" s="6"/>
     </row>
     <row r="119" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A119" s="46"/>
+      <c r="A119" s="80"/>
       <c r="B119" s="30" t="s">
         <v>161</v>
       </c>
@@ -5757,7 +5894,7 @@
       <c r="U119" s="6"/>
     </row>
     <row r="120" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A120" s="46"/>
+      <c r="A120" s="80"/>
       <c r="B120" s="30" t="s">
         <v>162</v>
       </c>
@@ -5788,7 +5925,7 @@
       <c r="U120" s="6"/>
     </row>
     <row r="121" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A121" s="46"/>
+      <c r="A121" s="80"/>
       <c r="B121" s="30" t="s">
         <v>163</v>
       </c>
@@ -5819,7 +5956,7 @@
       <c r="U121" s="6"/>
     </row>
     <row r="122" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A122" s="46"/>
+      <c r="A122" s="81"/>
       <c r="B122" s="30" t="s">
         <v>164</v>
       </c>
@@ -5850,7 +5987,7 @@
       <c r="U122" s="6"/>
     </row>
     <row r="123" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A123" s="53">
+      <c r="A123" s="72">
         <v>18</v>
       </c>
       <c r="B123" s="28" t="s">
@@ -5883,7 +6020,7 @@
       <c r="U123" s="16"/>
     </row>
     <row r="124" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A124" s="53"/>
+      <c r="A124" s="73"/>
       <c r="B124" s="28" t="s">
         <v>166</v>
       </c>
@@ -5914,7 +6051,7 @@
       <c r="U124" s="16"/>
     </row>
     <row r="125" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A125" s="53"/>
+      <c r="A125" s="73"/>
       <c r="B125" s="28" t="s">
         <v>167</v>
       </c>
@@ -5945,7 +6082,7 @@
       <c r="U125" s="16"/>
     </row>
     <row r="126" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A126" s="53"/>
+      <c r="A126" s="73"/>
       <c r="B126" s="28" t="s">
         <v>168</v>
       </c>
@@ -5976,14 +6113,14 @@
       <c r="U126" s="16"/>
     </row>
     <row r="127" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A127" s="53"/>
+      <c r="A127" s="73"/>
       <c r="B127" s="27" t="s">
         <v>169</v>
       </c>
       <c r="C127" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="D127" s="59" t="s">
+      <c r="D127" s="86" t="s">
         <v>69</v>
       </c>
       <c r="E127" s="59"/>
@@ -6005,7 +6142,7 @@
       <c r="U127" s="60"/>
     </row>
     <row r="128" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A128" s="53"/>
+      <c r="A128" s="73"/>
       <c r="B128" s="28" t="s">
         <v>170</v>
       </c>
@@ -6036,7 +6173,7 @@
       <c r="U128" s="16"/>
     </row>
     <row r="129" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A129" s="53"/>
+      <c r="A129" s="74"/>
       <c r="B129" s="28" t="s">
         <v>171</v>
       </c>
@@ -6067,7 +6204,7 @@
       <c r="U129" s="16"/>
     </row>
     <row r="130" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A130" s="46">
+      <c r="A130" s="79">
         <v>19</v>
       </c>
       <c r="B130" s="30" t="s">
@@ -6100,7 +6237,7 @@
       <c r="U130" s="6"/>
     </row>
     <row r="131" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A131" s="46"/>
+      <c r="A131" s="80"/>
       <c r="B131" s="30" t="s">
         <v>173</v>
       </c>
@@ -6131,7 +6268,7 @@
       <c r="U131" s="6"/>
     </row>
     <row r="132" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A132" s="46"/>
+      <c r="A132" s="80"/>
       <c r="B132" s="30" t="s">
         <v>174</v>
       </c>
@@ -6162,7 +6299,7 @@
       <c r="U132" s="6"/>
     </row>
     <row r="133" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A133" s="46"/>
+      <c r="A133" s="80"/>
       <c r="B133" s="30" t="s">
         <v>175</v>
       </c>
@@ -6193,7 +6330,7 @@
       <c r="U133" s="6"/>
     </row>
     <row r="134" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A134" s="46"/>
+      <c r="A134" s="80"/>
       <c r="B134" s="30" t="s">
         <v>176</v>
       </c>
@@ -6224,7 +6361,7 @@
       <c r="U134" s="6"/>
     </row>
     <row r="135" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A135" s="46"/>
+      <c r="A135" s="80"/>
       <c r="B135" s="30" t="s">
         <v>177</v>
       </c>
@@ -6255,7 +6392,7 @@
       <c r="U135" s="6"/>
     </row>
     <row r="136" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A136" s="46"/>
+      <c r="A136" s="81"/>
       <c r="B136" s="30" t="s">
         <v>178</v>
       </c>

--- a/raw/Timetable_2026Autumn_2025IE.xlsx
+++ b/raw/Timetable_2026Autumn_2025IE.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30502"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8988D75C-C13E-48B5-93E8-8A975F9210DD}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BD1E08B-32D0-49FF-9FCB-823B393C1849}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2025IE1" sheetId="2" r:id="rId1"/>
@@ -935,7 +935,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1069,9 +1069,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1094,6 +1091,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1135,19 +1135,22 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1159,25 +1162,22 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1186,13 +1186,7 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1549,74 +1543,74 @@
         <v>1</v>
       </c>
       <c r="C2" s="56"/>
-      <c r="D2" s="67" t="s">
+      <c r="D2" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="68"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="67" t="s">
+      <c r="E2" s="77"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="68"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="67" t="s">
+      <c r="H2" s="77"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="68"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="67" t="s">
+      <c r="K2" s="77"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="68"/>
-      <c r="O2" s="69"/>
-      <c r="P2" s="67" t="s">
+      <c r="N2" s="77"/>
+      <c r="O2" s="78"/>
+      <c r="P2" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="68"/>
-      <c r="R2" s="69"/>
-      <c r="S2" s="67" t="s">
+      <c r="Q2" s="77"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="T2" s="68"/>
-      <c r="U2" s="69"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="78"/>
     </row>
     <row r="3" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="71"/>
-      <c r="B3" s="70"/>
+      <c r="A3" s="79"/>
+      <c r="B3" s="80"/>
       <c r="C3" s="58"/>
-      <c r="D3" s="67" t="s">
+      <c r="D3" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="68"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="67" t="s">
+      <c r="E3" s="77"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="68"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="67" t="s">
+      <c r="H3" s="77"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="68"/>
-      <c r="L3" s="69"/>
-      <c r="M3" s="67" t="s">
+      <c r="K3" s="77"/>
+      <c r="L3" s="78"/>
+      <c r="M3" s="76" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="68"/>
-      <c r="O3" s="69"/>
-      <c r="P3" s="67" t="s">
+      <c r="N3" s="77"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="68"/>
-      <c r="R3" s="69"/>
-      <c r="S3" s="67" t="s">
+      <c r="Q3" s="77"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="68"/>
-      <c r="U3" s="69"/>
+      <c r="T3" s="77"/>
+      <c r="U3" s="78"/>
     </row>
     <row r="4" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="79">
+      <c r="A4" s="67">
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -1674,7 +1668,7 @@
       </c>
     </row>
     <row r="5" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A5" s="80"/>
+      <c r="A5" s="68"/>
       <c r="B5" s="2" t="s">
         <v>23</v>
       </c>
@@ -1720,7 +1714,7 @@
       </c>
     </row>
     <row r="6" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="80"/>
+      <c r="A6" s="68"/>
       <c r="B6" s="2" t="s">
         <v>25</v>
       </c>
@@ -1782,7 +1776,7 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="80"/>
+      <c r="A7" s="68"/>
       <c r="B7" s="2" t="s">
         <v>31</v>
       </c>
@@ -1846,7 +1840,7 @@
       </c>
     </row>
     <row r="8" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A8" s="80"/>
+      <c r="A8" s="68"/>
       <c r="B8" s="2" t="s">
         <v>36</v>
       </c>
@@ -1890,7 +1884,7 @@
       </c>
     </row>
     <row r="9" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="80"/>
+      <c r="A9" s="68"/>
       <c r="B9" s="2" t="s">
         <v>39</v>
       </c>
@@ -1934,7 +1928,7 @@
       </c>
     </row>
     <row r="10" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A10" s="81"/>
+      <c r="A10" s="69"/>
       <c r="B10" s="2" t="s">
         <v>43</v>
       </c>
@@ -1976,7 +1970,7 @@
       </c>
     </row>
     <row r="11" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A11" s="72">
+      <c r="A11" s="73">
         <v>2</v>
       </c>
       <c r="B11" s="13" t="s">
@@ -2042,7 +2036,7 @@
       </c>
     </row>
     <row r="12" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="73"/>
+      <c r="A12" s="74"/>
       <c r="B12" s="13" t="s">
         <v>47</v>
       </c>
@@ -2104,7 +2098,7 @@
       </c>
     </row>
     <row r="13" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="73"/>
+      <c r="A13" s="74"/>
       <c r="B13" s="13" t="s">
         <v>49</v>
       </c>
@@ -2156,7 +2150,7 @@
       <c r="AA13" s="3"/>
     </row>
     <row r="14" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="73"/>
+      <c r="A14" s="74"/>
       <c r="B14" s="13" t="s">
         <v>50</v>
       </c>
@@ -2220,7 +2214,7 @@
       <c r="AA14" s="3"/>
     </row>
     <row r="15" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="73"/>
+      <c r="A15" s="74"/>
       <c r="B15" s="13" t="s">
         <v>54</v>
       </c>
@@ -2272,7 +2266,7 @@
       <c r="AA15" s="3"/>
     </row>
     <row r="16" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="73"/>
+      <c r="A16" s="74"/>
       <c r="B16" s="13" t="s">
         <v>55</v>
       </c>
@@ -2299,7 +2293,7 @@
       <c r="U16" s="17"/>
     </row>
     <row r="17" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A17" s="74"/>
+      <c r="A17" s="75"/>
       <c r="B17" s="13" t="s">
         <v>56</v>
       </c>
@@ -2326,7 +2320,7 @@
       <c r="U17" s="17"/>
     </row>
     <row r="18" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A18" s="79">
+      <c r="A18" s="67">
         <v>3</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -2375,7 +2369,7 @@
       <c r="U18" s="6"/>
     </row>
     <row r="19" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A19" s="80"/>
+      <c r="A19" s="68"/>
       <c r="B19" s="2" t="s">
         <v>58</v>
       </c>
@@ -2422,7 +2416,7 @@
       <c r="U19" s="6"/>
     </row>
     <row r="20" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A20" s="80"/>
+      <c r="A20" s="68"/>
       <c r="B20" s="2" t="s">
         <v>59</v>
       </c>
@@ -2469,7 +2463,7 @@
       <c r="U20" s="6"/>
     </row>
     <row r="21" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A21" s="80"/>
+      <c r="A21" s="68"/>
       <c r="B21" s="2" t="s">
         <v>60</v>
       </c>
@@ -2528,7 +2522,7 @@
       </c>
     </row>
     <row r="22" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A22" s="80"/>
+      <c r="A22" s="68"/>
       <c r="B22" s="2" t="s">
         <v>61</v>
       </c>
@@ -2575,7 +2569,7 @@
       <c r="U22" s="6"/>
     </row>
     <row r="23" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A23" s="80"/>
+      <c r="A23" s="68"/>
       <c r="B23" s="2" t="s">
         <v>62</v>
       </c>
@@ -2602,7 +2596,7 @@
       <c r="U23" s="6"/>
     </row>
     <row r="24" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A24" s="81"/>
+      <c r="A24" s="69"/>
       <c r="B24" s="18" t="s">
         <v>63</v>
       </c>
@@ -2629,7 +2623,7 @@
       <c r="U24" s="22"/>
     </row>
     <row r="25" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A25" s="72">
+      <c r="A25" s="73">
         <v>4</v>
       </c>
       <c r="B25" s="13" t="s">
@@ -2678,7 +2672,7 @@
       <c r="U25" s="17"/>
     </row>
     <row r="26" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A26" s="73"/>
+      <c r="A26" s="74"/>
       <c r="B26" s="13" t="s">
         <v>65</v>
       </c>
@@ -2725,7 +2719,7 @@
       <c r="U26" s="17"/>
     </row>
     <row r="27" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A27" s="73"/>
+      <c r="A27" s="74"/>
       <c r="B27" s="13" t="s">
         <v>66</v>
       </c>
@@ -2772,7 +2766,7 @@
       <c r="U27" s="17"/>
     </row>
     <row r="28" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A28" s="73"/>
+      <c r="A28" s="74"/>
       <c r="B28" s="13" t="s">
         <v>67</v>
       </c>
@@ -2819,90 +2813,90 @@
       <c r="U28" s="17"/>
     </row>
     <row r="29" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A29" s="73"/>
+      <c r="A29" s="74"/>
       <c r="B29" s="25" t="s">
         <v>68</v>
       </c>
       <c r="C29" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="D29" s="76" t="s">
+      <c r="D29" s="71" t="s">
         <v>69</v>
       </c>
-      <c r="E29" s="77"/>
-      <c r="F29" s="77"/>
-      <c r="G29" s="77"/>
-      <c r="H29" s="77"/>
-      <c r="I29" s="77"/>
-      <c r="J29" s="77"/>
-      <c r="K29" s="77"/>
-      <c r="L29" s="77"/>
-      <c r="M29" s="77"/>
-      <c r="N29" s="77"/>
-      <c r="O29" s="77"/>
-      <c r="P29" s="77"/>
-      <c r="Q29" s="77"/>
-      <c r="R29" s="77"/>
-      <c r="S29" s="77"/>
-      <c r="T29" s="77"/>
-      <c r="U29" s="50"/>
+      <c r="E29" s="48"/>
+      <c r="F29" s="48"/>
+      <c r="G29" s="48"/>
+      <c r="H29" s="48"/>
+      <c r="I29" s="48"/>
+      <c r="J29" s="48"/>
+      <c r="K29" s="48"/>
+      <c r="L29" s="48"/>
+      <c r="M29" s="48"/>
+      <c r="N29" s="48"/>
+      <c r="O29" s="48"/>
+      <c r="P29" s="48"/>
+      <c r="Q29" s="48"/>
+      <c r="R29" s="48"/>
+      <c r="S29" s="48"/>
+      <c r="T29" s="48"/>
+      <c r="U29" s="49"/>
     </row>
     <row r="30" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A30" s="73"/>
+      <c r="A30" s="74"/>
       <c r="B30" s="25" t="s">
         <v>70</v>
       </c>
       <c r="C30" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="D30" s="76"/>
-      <c r="E30" s="77"/>
-      <c r="F30" s="77"/>
-      <c r="G30" s="77"/>
-      <c r="H30" s="77"/>
-      <c r="I30" s="77"/>
-      <c r="J30" s="77"/>
-      <c r="K30" s="77"/>
-      <c r="L30" s="77"/>
-      <c r="M30" s="77"/>
-      <c r="N30" s="77"/>
-      <c r="O30" s="77"/>
-      <c r="P30" s="77"/>
-      <c r="Q30" s="77"/>
-      <c r="R30" s="77"/>
-      <c r="S30" s="77"/>
-      <c r="T30" s="77"/>
-      <c r="U30" s="50"/>
+      <c r="D30" s="71"/>
+      <c r="E30" s="48"/>
+      <c r="F30" s="48"/>
+      <c r="G30" s="48"/>
+      <c r="H30" s="48"/>
+      <c r="I30" s="48"/>
+      <c r="J30" s="48"/>
+      <c r="K30" s="48"/>
+      <c r="L30" s="48"/>
+      <c r="M30" s="48"/>
+      <c r="N30" s="48"/>
+      <c r="O30" s="48"/>
+      <c r="P30" s="48"/>
+      <c r="Q30" s="48"/>
+      <c r="R30" s="48"/>
+      <c r="S30" s="48"/>
+      <c r="T30" s="48"/>
+      <c r="U30" s="49"/>
     </row>
     <row r="31" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A31" s="74"/>
+      <c r="A31" s="75"/>
       <c r="B31" s="25" t="s">
         <v>71</v>
       </c>
       <c r="C31" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="D31" s="78"/>
-      <c r="E31" s="51"/>
-      <c r="F31" s="51"/>
-      <c r="G31" s="51"/>
-      <c r="H31" s="51"/>
-      <c r="I31" s="51"/>
-      <c r="J31" s="51"/>
-      <c r="K31" s="51"/>
-      <c r="L31" s="51"/>
-      <c r="M31" s="51"/>
-      <c r="N31" s="51"/>
-      <c r="O31" s="51"/>
-      <c r="P31" s="51"/>
-      <c r="Q31" s="51"/>
-      <c r="R31" s="51"/>
-      <c r="S31" s="51"/>
-      <c r="T31" s="51"/>
-      <c r="U31" s="52"/>
+      <c r="D31" s="72"/>
+      <c r="E31" s="50"/>
+      <c r="F31" s="50"/>
+      <c r="G31" s="50"/>
+      <c r="H31" s="50"/>
+      <c r="I31" s="50"/>
+      <c r="J31" s="50"/>
+      <c r="K31" s="50"/>
+      <c r="L31" s="50"/>
+      <c r="M31" s="50"/>
+      <c r="N31" s="50"/>
+      <c r="O31" s="50"/>
+      <c r="P31" s="50"/>
+      <c r="Q31" s="50"/>
+      <c r="R31" s="50"/>
+      <c r="S31" s="50"/>
+      <c r="T31" s="50"/>
+      <c r="U31" s="51"/>
     </row>
     <row r="32" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A32" s="79">
+      <c r="A32" s="67">
         <v>5</v>
       </c>
       <c r="B32" s="2" t="s">
@@ -2951,7 +2945,7 @@
       <c r="U32" s="6"/>
     </row>
     <row r="33" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A33" s="80"/>
+      <c r="A33" s="68"/>
       <c r="B33" s="2" t="s">
         <v>73</v>
       </c>
@@ -2998,7 +2992,7 @@
       <c r="U33" s="6"/>
     </row>
     <row r="34" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A34" s="80"/>
+      <c r="A34" s="68"/>
       <c r="B34" s="2" t="s">
         <v>74</v>
       </c>
@@ -3045,117 +3039,117 @@
       <c r="U34" s="6"/>
     </row>
     <row r="35" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A35" s="80"/>
+      <c r="A35" s="68"/>
       <c r="B35" s="27" t="s">
         <v>75</v>
       </c>
       <c r="C35" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="D35" s="75" t="s">
+      <c r="D35" s="70" t="s">
         <v>69</v>
       </c>
-      <c r="E35" s="47"/>
-      <c r="F35" s="47"/>
-      <c r="G35" s="47"/>
-      <c r="H35" s="47"/>
-      <c r="I35" s="47"/>
-      <c r="J35" s="47"/>
-      <c r="K35" s="47"/>
-      <c r="L35" s="47"/>
-      <c r="M35" s="47"/>
-      <c r="N35" s="47"/>
-      <c r="O35" s="47"/>
-      <c r="P35" s="47"/>
-      <c r="Q35" s="47"/>
-      <c r="R35" s="47"/>
-      <c r="S35" s="47"/>
-      <c r="T35" s="47"/>
-      <c r="U35" s="48"/>
+      <c r="E35" s="46"/>
+      <c r="F35" s="46"/>
+      <c r="G35" s="46"/>
+      <c r="H35" s="46"/>
+      <c r="I35" s="46"/>
+      <c r="J35" s="46"/>
+      <c r="K35" s="46"/>
+      <c r="L35" s="46"/>
+      <c r="M35" s="46"/>
+      <c r="N35" s="46"/>
+      <c r="O35" s="46"/>
+      <c r="P35" s="46"/>
+      <c r="Q35" s="46"/>
+      <c r="R35" s="46"/>
+      <c r="S35" s="46"/>
+      <c r="T35" s="46"/>
+      <c r="U35" s="47"/>
     </row>
     <row r="36" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A36" s="80"/>
+      <c r="A36" s="68"/>
       <c r="B36" s="27" t="s">
         <v>76</v>
       </c>
       <c r="C36" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="D36" s="76"/>
-      <c r="E36" s="77"/>
-      <c r="F36" s="77"/>
-      <c r="G36" s="77"/>
-      <c r="H36" s="77"/>
-      <c r="I36" s="77"/>
-      <c r="J36" s="77"/>
-      <c r="K36" s="77"/>
-      <c r="L36" s="77"/>
-      <c r="M36" s="77"/>
-      <c r="N36" s="77"/>
-      <c r="O36" s="77"/>
-      <c r="P36" s="77"/>
-      <c r="Q36" s="77"/>
-      <c r="R36" s="77"/>
-      <c r="S36" s="77"/>
-      <c r="T36" s="77"/>
-      <c r="U36" s="50"/>
+      <c r="D36" s="71"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="48"/>
+      <c r="H36" s="48"/>
+      <c r="I36" s="48"/>
+      <c r="J36" s="48"/>
+      <c r="K36" s="48"/>
+      <c r="L36" s="48"/>
+      <c r="M36" s="48"/>
+      <c r="N36" s="48"/>
+      <c r="O36" s="48"/>
+      <c r="P36" s="48"/>
+      <c r="Q36" s="48"/>
+      <c r="R36" s="48"/>
+      <c r="S36" s="48"/>
+      <c r="T36" s="48"/>
+      <c r="U36" s="49"/>
     </row>
     <row r="37" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A37" s="80"/>
+      <c r="A37" s="68"/>
       <c r="B37" s="27" t="s">
         <v>77</v>
       </c>
       <c r="C37" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="D37" s="76"/>
-      <c r="E37" s="77"/>
-      <c r="F37" s="77"/>
-      <c r="G37" s="77"/>
-      <c r="H37" s="77"/>
-      <c r="I37" s="77"/>
-      <c r="J37" s="77"/>
-      <c r="K37" s="77"/>
-      <c r="L37" s="77"/>
-      <c r="M37" s="77"/>
-      <c r="N37" s="77"/>
-      <c r="O37" s="77"/>
-      <c r="P37" s="77"/>
-      <c r="Q37" s="77"/>
-      <c r="R37" s="77"/>
-      <c r="S37" s="77"/>
-      <c r="T37" s="77"/>
-      <c r="U37" s="50"/>
+      <c r="D37" s="71"/>
+      <c r="E37" s="48"/>
+      <c r="F37" s="48"/>
+      <c r="G37" s="48"/>
+      <c r="H37" s="48"/>
+      <c r="I37" s="48"/>
+      <c r="J37" s="48"/>
+      <c r="K37" s="48"/>
+      <c r="L37" s="48"/>
+      <c r="M37" s="48"/>
+      <c r="N37" s="48"/>
+      <c r="O37" s="48"/>
+      <c r="P37" s="48"/>
+      <c r="Q37" s="48"/>
+      <c r="R37" s="48"/>
+      <c r="S37" s="48"/>
+      <c r="T37" s="48"/>
+      <c r="U37" s="49"/>
     </row>
     <row r="38" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A38" s="81"/>
+      <c r="A38" s="69"/>
       <c r="B38" s="27" t="s">
         <v>78</v>
       </c>
       <c r="C38" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="D38" s="76"/>
-      <c r="E38" s="77"/>
-      <c r="F38" s="77"/>
-      <c r="G38" s="77"/>
-      <c r="H38" s="77"/>
-      <c r="I38" s="77"/>
-      <c r="J38" s="77"/>
-      <c r="K38" s="77"/>
-      <c r="L38" s="77"/>
-      <c r="M38" s="77"/>
-      <c r="N38" s="77"/>
-      <c r="O38" s="77"/>
-      <c r="P38" s="77"/>
-      <c r="Q38" s="77"/>
-      <c r="R38" s="77"/>
-      <c r="S38" s="77"/>
-      <c r="T38" s="77"/>
-      <c r="U38" s="50"/>
+      <c r="D38" s="71"/>
+      <c r="E38" s="48"/>
+      <c r="F38" s="48"/>
+      <c r="G38" s="48"/>
+      <c r="H38" s="48"/>
+      <c r="I38" s="48"/>
+      <c r="J38" s="48"/>
+      <c r="K38" s="48"/>
+      <c r="L38" s="48"/>
+      <c r="M38" s="48"/>
+      <c r="N38" s="48"/>
+      <c r="O38" s="48"/>
+      <c r="P38" s="48"/>
+      <c r="Q38" s="48"/>
+      <c r="R38" s="48"/>
+      <c r="S38" s="48"/>
+      <c r="T38" s="48"/>
+      <c r="U38" s="49"/>
     </row>
     <row r="39" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A39" s="72">
+      <c r="A39" s="73">
         <v>6</v>
       </c>
       <c r="B39" s="27" t="s">
@@ -3164,81 +3158,81 @@
       <c r="C39" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="76"/>
-      <c r="E39" s="77"/>
-      <c r="F39" s="77"/>
-      <c r="G39" s="77"/>
-      <c r="H39" s="77"/>
-      <c r="I39" s="77"/>
-      <c r="J39" s="77"/>
-      <c r="K39" s="77"/>
-      <c r="L39" s="77"/>
-      <c r="M39" s="77"/>
-      <c r="N39" s="77"/>
-      <c r="O39" s="77"/>
-      <c r="P39" s="77"/>
-      <c r="Q39" s="77"/>
-      <c r="R39" s="77"/>
-      <c r="S39" s="77"/>
-      <c r="T39" s="77"/>
-      <c r="U39" s="50"/>
+      <c r="D39" s="71"/>
+      <c r="E39" s="48"/>
+      <c r="F39" s="48"/>
+      <c r="G39" s="48"/>
+      <c r="H39" s="48"/>
+      <c r="I39" s="48"/>
+      <c r="J39" s="48"/>
+      <c r="K39" s="48"/>
+      <c r="L39" s="48"/>
+      <c r="M39" s="48"/>
+      <c r="N39" s="48"/>
+      <c r="O39" s="48"/>
+      <c r="P39" s="48"/>
+      <c r="Q39" s="48"/>
+      <c r="R39" s="48"/>
+      <c r="S39" s="48"/>
+      <c r="T39" s="48"/>
+      <c r="U39" s="49"/>
     </row>
     <row r="40" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A40" s="73"/>
+      <c r="A40" s="74"/>
       <c r="B40" s="27" t="s">
         <v>80</v>
       </c>
       <c r="C40" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="D40" s="76"/>
-      <c r="E40" s="77"/>
-      <c r="F40" s="77"/>
-      <c r="G40" s="77"/>
-      <c r="H40" s="77"/>
-      <c r="I40" s="77"/>
-      <c r="J40" s="77"/>
-      <c r="K40" s="77"/>
-      <c r="L40" s="77"/>
-      <c r="M40" s="77"/>
-      <c r="N40" s="77"/>
-      <c r="O40" s="77"/>
-      <c r="P40" s="77"/>
-      <c r="Q40" s="77"/>
-      <c r="R40" s="77"/>
-      <c r="S40" s="77"/>
-      <c r="T40" s="77"/>
-      <c r="U40" s="50"/>
+      <c r="D40" s="71"/>
+      <c r="E40" s="48"/>
+      <c r="F40" s="48"/>
+      <c r="G40" s="48"/>
+      <c r="H40" s="48"/>
+      <c r="I40" s="48"/>
+      <c r="J40" s="48"/>
+      <c r="K40" s="48"/>
+      <c r="L40" s="48"/>
+      <c r="M40" s="48"/>
+      <c r="N40" s="48"/>
+      <c r="O40" s="48"/>
+      <c r="P40" s="48"/>
+      <c r="Q40" s="48"/>
+      <c r="R40" s="48"/>
+      <c r="S40" s="48"/>
+      <c r="T40" s="48"/>
+      <c r="U40" s="49"/>
     </row>
     <row r="41" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A41" s="73"/>
+      <c r="A41" s="74"/>
       <c r="B41" s="27" t="s">
         <v>81</v>
       </c>
       <c r="C41" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="D41" s="78"/>
-      <c r="E41" s="51"/>
-      <c r="F41" s="51"/>
-      <c r="G41" s="51"/>
-      <c r="H41" s="51"/>
-      <c r="I41" s="51"/>
-      <c r="J41" s="51"/>
-      <c r="K41" s="51"/>
-      <c r="L41" s="51"/>
-      <c r="M41" s="51"/>
-      <c r="N41" s="51"/>
-      <c r="O41" s="51"/>
-      <c r="P41" s="51"/>
-      <c r="Q41" s="51"/>
-      <c r="R41" s="51"/>
-      <c r="S41" s="51"/>
-      <c r="T41" s="51"/>
-      <c r="U41" s="52"/>
+      <c r="D41" s="72"/>
+      <c r="E41" s="50"/>
+      <c r="F41" s="50"/>
+      <c r="G41" s="50"/>
+      <c r="H41" s="50"/>
+      <c r="I41" s="50"/>
+      <c r="J41" s="50"/>
+      <c r="K41" s="50"/>
+      <c r="L41" s="50"/>
+      <c r="M41" s="50"/>
+      <c r="N41" s="50"/>
+      <c r="O41" s="50"/>
+      <c r="P41" s="50"/>
+      <c r="Q41" s="50"/>
+      <c r="R41" s="50"/>
+      <c r="S41" s="50"/>
+      <c r="T41" s="50"/>
+      <c r="U41" s="51"/>
     </row>
     <row r="42" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A42" s="73"/>
+      <c r="A42" s="74"/>
       <c r="B42" s="28" t="s">
         <v>82</v>
       </c>
@@ -3297,7 +3291,7 @@
       </c>
     </row>
     <row r="43" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A43" s="73"/>
+      <c r="A43" s="74"/>
       <c r="B43" s="28" t="s">
         <v>83</v>
       </c>
@@ -3326,7 +3320,7 @@
       <c r="U43" s="17"/>
     </row>
     <row r="44" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A44" s="73"/>
+      <c r="A44" s="74"/>
       <c r="B44" s="29" t="s">
         <v>84</v>
       </c>
@@ -3353,7 +3347,7 @@
       <c r="U44" s="22"/>
     </row>
     <row r="45" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A45" s="74"/>
+      <c r="A45" s="75"/>
       <c r="B45" s="28" t="s">
         <v>85</v>
       </c>
@@ -3380,7 +3374,7 @@
       <c r="U45" s="17"/>
     </row>
     <row r="46" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A46" s="79">
+      <c r="A46" s="67">
         <v>7</v>
       </c>
       <c r="B46" s="30" t="s">
@@ -3429,7 +3423,7 @@
       <c r="U46" s="6"/>
     </row>
     <row r="47" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A47" s="80"/>
+      <c r="A47" s="68"/>
       <c r="B47" s="30" t="s">
         <v>87</v>
       </c>
@@ -3476,7 +3470,7 @@
       <c r="U47" s="6"/>
     </row>
     <row r="48" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A48" s="80"/>
+      <c r="A48" s="68"/>
       <c r="B48" s="30" t="s">
         <v>88</v>
       </c>
@@ -3523,7 +3517,7 @@
       <c r="U48" s="6"/>
     </row>
     <row r="49" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A49" s="80"/>
+      <c r="A49" s="68"/>
       <c r="B49" s="30" t="s">
         <v>89</v>
       </c>
@@ -3570,7 +3564,7 @@
       <c r="U49" s="6"/>
     </row>
     <row r="50" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A50" s="80"/>
+      <c r="A50" s="68"/>
       <c r="B50" s="30" t="s">
         <v>90</v>
       </c>
@@ -3617,7 +3611,7 @@
       <c r="U50" s="6"/>
     </row>
     <row r="51" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A51" s="80"/>
+      <c r="A51" s="68"/>
       <c r="B51" s="30" t="s">
         <v>91</v>
       </c>
@@ -3644,7 +3638,7 @@
       <c r="U51" s="6"/>
     </row>
     <row r="52" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A52" s="81"/>
+      <c r="A52" s="69"/>
       <c r="B52" s="30" t="s">
         <v>92</v>
       </c>
@@ -3671,7 +3665,7 @@
       <c r="U52" s="6"/>
     </row>
     <row r="53" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A53" s="72">
+      <c r="A53" s="73">
         <v>8</v>
       </c>
       <c r="B53" s="28" t="s">
@@ -3720,7 +3714,7 @@
       <c r="U53" s="17"/>
     </row>
     <row r="54" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A54" s="73"/>
+      <c r="A54" s="74"/>
       <c r="B54" s="28" t="s">
         <v>94</v>
       </c>
@@ -3767,7 +3761,7 @@
       <c r="U54" s="17"/>
     </row>
     <row r="55" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A55" s="73"/>
+      <c r="A55" s="74"/>
       <c r="B55" s="28" t="s">
         <v>95</v>
       </c>
@@ -3814,7 +3808,7 @@
       <c r="U55" s="17"/>
     </row>
     <row r="56" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A56" s="73"/>
+      <c r="A56" s="74"/>
       <c r="B56" s="28" t="s">
         <v>96</v>
       </c>
@@ -3873,7 +3867,7 @@
       </c>
     </row>
     <row r="57" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A57" s="73"/>
+      <c r="A57" s="74"/>
       <c r="B57" s="28" t="s">
         <v>97</v>
       </c>
@@ -3920,7 +3914,7 @@
       <c r="U57" s="17"/>
     </row>
     <row r="58" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A58" s="73"/>
+      <c r="A58" s="74"/>
       <c r="B58" s="28" t="s">
         <v>98</v>
       </c>
@@ -3930,15 +3924,15 @@
       <c r="D58" s="15"/>
       <c r="E58" s="15"/>
       <c r="F58" s="16"/>
-      <c r="G58" s="13"/>
+      <c r="G58" s="15"/>
       <c r="H58" s="15"/>
       <c r="I58" s="17"/>
-      <c r="J58" s="13"/>
+      <c r="J58" s="15"/>
       <c r="K58" s="15"/>
       <c r="L58" s="17"/>
-      <c r="M58" s="13"/>
+      <c r="M58" s="15"/>
       <c r="N58" s="15"/>
-      <c r="O58" s="17"/>
+      <c r="O58" s="15"/>
       <c r="P58" s="13"/>
       <c r="Q58" s="15"/>
       <c r="R58" s="17"/>
@@ -3947,7 +3941,7 @@
       <c r="U58" s="17"/>
     </row>
     <row r="59" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A59" s="74"/>
+      <c r="A59" s="75"/>
       <c r="B59" s="28" t="s">
         <v>99</v>
       </c>
@@ -3974,7 +3968,7 @@
       <c r="U59" s="17"/>
     </row>
     <row r="60" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A60" s="79">
+      <c r="A60" s="67">
         <v>9</v>
       </c>
       <c r="B60" s="30" t="s">
@@ -4023,7 +4017,7 @@
       <c r="U60" s="6"/>
     </row>
     <row r="61" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A61" s="80"/>
+      <c r="A61" s="68"/>
       <c r="B61" s="30" t="s">
         <v>101</v>
       </c>
@@ -4052,7 +4046,7 @@
       <c r="U61" s="6"/>
     </row>
     <row r="62" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A62" s="80"/>
+      <c r="A62" s="68"/>
       <c r="B62" s="30" t="s">
         <v>102</v>
       </c>
@@ -4099,7 +4093,7 @@
       <c r="U62" s="6"/>
     </row>
     <row r="63" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A63" s="80"/>
+      <c r="A63" s="68"/>
       <c r="B63" s="30" t="s">
         <v>103</v>
       </c>
@@ -4158,7 +4152,7 @@
       </c>
     </row>
     <row r="64" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A64" s="80"/>
+      <c r="A64" s="68"/>
       <c r="B64" s="30" t="s">
         <v>104</v>
       </c>
@@ -4187,7 +4181,7 @@
       <c r="U64" s="5"/>
     </row>
     <row r="65" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A65" s="80"/>
+      <c r="A65" s="68"/>
       <c r="B65" s="30" t="s">
         <v>105</v>
       </c>
@@ -4214,7 +4208,7 @@
       <c r="U65" s="5"/>
     </row>
     <row r="66" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A66" s="81"/>
+      <c r="A66" s="69"/>
       <c r="B66" s="30" t="s">
         <v>106</v>
       </c>
@@ -4241,7 +4235,7 @@
       <c r="U66" s="5"/>
     </row>
     <row r="67" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A67" s="72">
+      <c r="A67" s="73">
         <v>10</v>
       </c>
       <c r="B67" s="28" t="s">
@@ -4290,7 +4284,7 @@
       <c r="U67" s="16"/>
     </row>
     <row r="68" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A68" s="73"/>
+      <c r="A68" s="74"/>
       <c r="B68" s="28" t="s">
         <v>108</v>
       </c>
@@ -4319,7 +4313,7 @@
       <c r="U68" s="16"/>
     </row>
     <row r="69" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A69" s="73"/>
+      <c r="A69" s="74"/>
       <c r="B69" s="28" t="s">
         <v>109</v>
       </c>
@@ -4348,7 +4342,7 @@
       <c r="U69" s="16"/>
     </row>
     <row r="70" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A70" s="73"/>
+      <c r="A70" s="74"/>
       <c r="B70" s="28" t="s">
         <v>110</v>
       </c>
@@ -4407,7 +4401,7 @@
       </c>
     </row>
     <row r="71" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A71" s="73"/>
+      <c r="A71" s="74"/>
       <c r="B71" s="28" t="s">
         <v>111</v>
       </c>
@@ -4436,7 +4430,7 @@
       <c r="U71" s="16"/>
     </row>
     <row r="72" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A72" s="73"/>
+      <c r="A72" s="74"/>
       <c r="B72" s="28" t="s">
         <v>112</v>
       </c>
@@ -4463,7 +4457,7 @@
       <c r="U72" s="16"/>
     </row>
     <row r="73" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A73" s="74"/>
+      <c r="A73" s="75"/>
       <c r="B73" s="28" t="s">
         <v>113</v>
       </c>
@@ -4490,7 +4484,7 @@
       <c r="U73" s="16"/>
     </row>
     <row r="74" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A74" s="79">
+      <c r="A74" s="67">
         <v>11</v>
       </c>
       <c r="B74" s="30" t="s">
@@ -4539,7 +4533,7 @@
       <c r="U74" s="5"/>
     </row>
     <row r="75" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A75" s="80"/>
+      <c r="A75" s="68"/>
       <c r="B75" s="30" t="s">
         <v>115</v>
       </c>
@@ -4568,7 +4562,7 @@
       <c r="U75" s="5"/>
     </row>
     <row r="76" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A76" s="80"/>
+      <c r="A76" s="68"/>
       <c r="B76" s="30" t="s">
         <v>116</v>
       </c>
@@ -4597,7 +4591,7 @@
       <c r="U76" s="5"/>
     </row>
     <row r="77" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A77" s="80"/>
+      <c r="A77" s="68"/>
       <c r="B77" s="30" t="s">
         <v>117</v>
       </c>
@@ -4644,7 +4638,7 @@
       <c r="U77" s="6"/>
     </row>
     <row r="78" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A78" s="80"/>
+      <c r="A78" s="68"/>
       <c r="B78" s="30" t="s">
         <v>118</v>
       </c>
@@ -4673,7 +4667,7 @@
       <c r="U78" s="6"/>
     </row>
     <row r="79" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A79" s="80"/>
+      <c r="A79" s="68"/>
       <c r="B79" s="30" t="s">
         <v>119</v>
       </c>
@@ -4700,7 +4694,7 @@
       <c r="U79" s="6"/>
     </row>
     <row r="80" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A80" s="81"/>
+      <c r="A80" s="69"/>
       <c r="B80" s="30" t="s">
         <v>120</v>
       </c>
@@ -4727,7 +4721,7 @@
       <c r="U80" s="6"/>
     </row>
     <row r="81" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A81" s="72">
+      <c r="A81" s="73">
         <v>12</v>
       </c>
       <c r="B81" s="28" t="s">
@@ -4758,7 +4752,7 @@
       <c r="U81" s="62"/>
     </row>
     <row r="82" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A82" s="73"/>
+      <c r="A82" s="74"/>
       <c r="B82" s="28" t="s">
         <v>123</v>
       </c>
@@ -4766,26 +4760,26 @@
         <v>24</v>
       </c>
       <c r="D82" s="83"/>
-      <c r="E82" s="84"/>
-      <c r="F82" s="84"/>
-      <c r="G82" s="84"/>
-      <c r="H82" s="84"/>
-      <c r="I82" s="84"/>
-      <c r="J82" s="84"/>
-      <c r="K82" s="84"/>
-      <c r="L82" s="84"/>
-      <c r="M82" s="84"/>
-      <c r="N82" s="84"/>
-      <c r="O82" s="84"/>
-      <c r="P82" s="84"/>
-      <c r="Q82" s="84"/>
-      <c r="R82" s="84"/>
-      <c r="S82" s="84"/>
-      <c r="T82" s="84"/>
+      <c r="E82" s="63"/>
+      <c r="F82" s="63"/>
+      <c r="G82" s="63"/>
+      <c r="H82" s="63"/>
+      <c r="I82" s="63"/>
+      <c r="J82" s="63"/>
+      <c r="K82" s="63"/>
+      <c r="L82" s="63"/>
+      <c r="M82" s="63"/>
+      <c r="N82" s="63"/>
+      <c r="O82" s="63"/>
+      <c r="P82" s="63"/>
+      <c r="Q82" s="63"/>
+      <c r="R82" s="63"/>
+      <c r="S82" s="63"/>
+      <c r="T82" s="63"/>
       <c r="U82" s="64"/>
     </row>
     <row r="83" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A83" s="73"/>
+      <c r="A83" s="74"/>
       <c r="B83" s="28" t="s">
         <v>124</v>
       </c>
@@ -4793,26 +4787,26 @@
         <v>26</v>
       </c>
       <c r="D83" s="83"/>
-      <c r="E83" s="84"/>
-      <c r="F83" s="84"/>
-      <c r="G83" s="84"/>
-      <c r="H83" s="84"/>
-      <c r="I83" s="84"/>
-      <c r="J83" s="84"/>
-      <c r="K83" s="84"/>
-      <c r="L83" s="84"/>
-      <c r="M83" s="84"/>
-      <c r="N83" s="84"/>
-      <c r="O83" s="84"/>
-      <c r="P83" s="84"/>
-      <c r="Q83" s="84"/>
-      <c r="R83" s="84"/>
-      <c r="S83" s="84"/>
-      <c r="T83" s="84"/>
+      <c r="E83" s="63"/>
+      <c r="F83" s="63"/>
+      <c r="G83" s="63"/>
+      <c r="H83" s="63"/>
+      <c r="I83" s="63"/>
+      <c r="J83" s="63"/>
+      <c r="K83" s="63"/>
+      <c r="L83" s="63"/>
+      <c r="M83" s="63"/>
+      <c r="N83" s="63"/>
+      <c r="O83" s="63"/>
+      <c r="P83" s="63"/>
+      <c r="Q83" s="63"/>
+      <c r="R83" s="63"/>
+      <c r="S83" s="63"/>
+      <c r="T83" s="63"/>
       <c r="U83" s="64"/>
     </row>
     <row r="84" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A84" s="73"/>
+      <c r="A84" s="74"/>
       <c r="B84" s="28" t="s">
         <v>125</v>
       </c>
@@ -4820,26 +4814,26 @@
         <v>32</v>
       </c>
       <c r="D84" s="83"/>
-      <c r="E84" s="84"/>
-      <c r="F84" s="84"/>
-      <c r="G84" s="84"/>
-      <c r="H84" s="84"/>
-      <c r="I84" s="84"/>
-      <c r="J84" s="84"/>
-      <c r="K84" s="84"/>
-      <c r="L84" s="84"/>
-      <c r="M84" s="84"/>
-      <c r="N84" s="84"/>
-      <c r="O84" s="84"/>
-      <c r="P84" s="84"/>
-      <c r="Q84" s="84"/>
-      <c r="R84" s="84"/>
-      <c r="S84" s="84"/>
-      <c r="T84" s="84"/>
+      <c r="E84" s="63"/>
+      <c r="F84" s="63"/>
+      <c r="G84" s="63"/>
+      <c r="H84" s="63"/>
+      <c r="I84" s="63"/>
+      <c r="J84" s="63"/>
+      <c r="K84" s="63"/>
+      <c r="L84" s="63"/>
+      <c r="M84" s="63"/>
+      <c r="N84" s="63"/>
+      <c r="O84" s="63"/>
+      <c r="P84" s="63"/>
+      <c r="Q84" s="63"/>
+      <c r="R84" s="63"/>
+      <c r="S84" s="63"/>
+      <c r="T84" s="63"/>
       <c r="U84" s="64"/>
     </row>
     <row r="85" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A85" s="73"/>
+      <c r="A85" s="74"/>
       <c r="B85" s="28" t="s">
         <v>126</v>
       </c>
@@ -4847,26 +4841,26 @@
         <v>37</v>
       </c>
       <c r="D85" s="83"/>
-      <c r="E85" s="84"/>
-      <c r="F85" s="84"/>
-      <c r="G85" s="84"/>
-      <c r="H85" s="84"/>
-      <c r="I85" s="84"/>
-      <c r="J85" s="84"/>
-      <c r="K85" s="84"/>
-      <c r="L85" s="84"/>
-      <c r="M85" s="84"/>
-      <c r="N85" s="84"/>
-      <c r="O85" s="84"/>
-      <c r="P85" s="84"/>
-      <c r="Q85" s="84"/>
-      <c r="R85" s="84"/>
-      <c r="S85" s="84"/>
-      <c r="T85" s="84"/>
+      <c r="E85" s="63"/>
+      <c r="F85" s="63"/>
+      <c r="G85" s="63"/>
+      <c r="H85" s="63"/>
+      <c r="I85" s="63"/>
+      <c r="J85" s="63"/>
+      <c r="K85" s="63"/>
+      <c r="L85" s="63"/>
+      <c r="M85" s="63"/>
+      <c r="N85" s="63"/>
+      <c r="O85" s="63"/>
+      <c r="P85" s="63"/>
+      <c r="Q85" s="63"/>
+      <c r="R85" s="63"/>
+      <c r="S85" s="63"/>
+      <c r="T85" s="63"/>
       <c r="U85" s="64"/>
     </row>
     <row r="86" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A86" s="73"/>
+      <c r="A86" s="74"/>
       <c r="B86" s="28" t="s">
         <v>127</v>
       </c>
@@ -4874,26 +4868,26 @@
         <v>40</v>
       </c>
       <c r="D86" s="83"/>
-      <c r="E86" s="84"/>
-      <c r="F86" s="84"/>
-      <c r="G86" s="84"/>
-      <c r="H86" s="84"/>
-      <c r="I86" s="84"/>
-      <c r="J86" s="84"/>
-      <c r="K86" s="84"/>
-      <c r="L86" s="84"/>
-      <c r="M86" s="84"/>
-      <c r="N86" s="84"/>
-      <c r="O86" s="84"/>
-      <c r="P86" s="84"/>
-      <c r="Q86" s="84"/>
-      <c r="R86" s="84"/>
-      <c r="S86" s="84"/>
-      <c r="T86" s="84"/>
+      <c r="E86" s="63"/>
+      <c r="F86" s="63"/>
+      <c r="G86" s="63"/>
+      <c r="H86" s="63"/>
+      <c r="I86" s="63"/>
+      <c r="J86" s="63"/>
+      <c r="K86" s="63"/>
+      <c r="L86" s="63"/>
+      <c r="M86" s="63"/>
+      <c r="N86" s="63"/>
+      <c r="O86" s="63"/>
+      <c r="P86" s="63"/>
+      <c r="Q86" s="63"/>
+      <c r="R86" s="63"/>
+      <c r="S86" s="63"/>
+      <c r="T86" s="63"/>
       <c r="U86" s="64"/>
     </row>
     <row r="87" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A87" s="74"/>
+      <c r="A87" s="75"/>
       <c r="B87" s="28" t="s">
         <v>128</v>
       </c>
@@ -4901,26 +4895,26 @@
         <v>44</v>
       </c>
       <c r="D87" s="83"/>
-      <c r="E87" s="84"/>
-      <c r="F87" s="84"/>
-      <c r="G87" s="84"/>
-      <c r="H87" s="84"/>
-      <c r="I87" s="84"/>
-      <c r="J87" s="84"/>
-      <c r="K87" s="84"/>
-      <c r="L87" s="84"/>
-      <c r="M87" s="84"/>
-      <c r="N87" s="84"/>
-      <c r="O87" s="84"/>
-      <c r="P87" s="84"/>
-      <c r="Q87" s="84"/>
-      <c r="R87" s="84"/>
-      <c r="S87" s="84"/>
-      <c r="T87" s="84"/>
+      <c r="E87" s="63"/>
+      <c r="F87" s="63"/>
+      <c r="G87" s="63"/>
+      <c r="H87" s="63"/>
+      <c r="I87" s="63"/>
+      <c r="J87" s="63"/>
+      <c r="K87" s="63"/>
+      <c r="L87" s="63"/>
+      <c r="M87" s="63"/>
+      <c r="N87" s="63"/>
+      <c r="O87" s="63"/>
+      <c r="P87" s="63"/>
+      <c r="Q87" s="63"/>
+      <c r="R87" s="63"/>
+      <c r="S87" s="63"/>
+      <c r="T87" s="63"/>
       <c r="U87" s="64"/>
     </row>
     <row r="88" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A88" s="79">
+      <c r="A88" s="67">
         <v>13</v>
       </c>
       <c r="B88" s="30" t="s">
@@ -4930,26 +4924,26 @@
         <v>15</v>
       </c>
       <c r="D88" s="83"/>
-      <c r="E88" s="84"/>
-      <c r="F88" s="84"/>
-      <c r="G88" s="84"/>
-      <c r="H88" s="84"/>
-      <c r="I88" s="84"/>
-      <c r="J88" s="84"/>
-      <c r="K88" s="84"/>
-      <c r="L88" s="84"/>
-      <c r="M88" s="84"/>
-      <c r="N88" s="84"/>
-      <c r="O88" s="84"/>
-      <c r="P88" s="84"/>
-      <c r="Q88" s="84"/>
-      <c r="R88" s="84"/>
-      <c r="S88" s="84"/>
-      <c r="T88" s="84"/>
+      <c r="E88" s="63"/>
+      <c r="F88" s="63"/>
+      <c r="G88" s="63"/>
+      <c r="H88" s="63"/>
+      <c r="I88" s="63"/>
+      <c r="J88" s="63"/>
+      <c r="K88" s="63"/>
+      <c r="L88" s="63"/>
+      <c r="M88" s="63"/>
+      <c r="N88" s="63"/>
+      <c r="O88" s="63"/>
+      <c r="P88" s="63"/>
+      <c r="Q88" s="63"/>
+      <c r="R88" s="63"/>
+      <c r="S88" s="63"/>
+      <c r="T88" s="63"/>
       <c r="U88" s="64"/>
     </row>
     <row r="89" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A89" s="80"/>
+      <c r="A89" s="68"/>
       <c r="B89" s="30" t="s">
         <v>130</v>
       </c>
@@ -4957,26 +4951,26 @@
         <v>24</v>
       </c>
       <c r="D89" s="83"/>
-      <c r="E89" s="84"/>
-      <c r="F89" s="84"/>
-      <c r="G89" s="84"/>
-      <c r="H89" s="84"/>
-      <c r="I89" s="84"/>
-      <c r="J89" s="84"/>
-      <c r="K89" s="84"/>
-      <c r="L89" s="84"/>
-      <c r="M89" s="84"/>
-      <c r="N89" s="84"/>
-      <c r="O89" s="84"/>
-      <c r="P89" s="84"/>
-      <c r="Q89" s="84"/>
-      <c r="R89" s="84"/>
-      <c r="S89" s="84"/>
-      <c r="T89" s="84"/>
+      <c r="E89" s="63"/>
+      <c r="F89" s="63"/>
+      <c r="G89" s="63"/>
+      <c r="H89" s="63"/>
+      <c r="I89" s="63"/>
+      <c r="J89" s="63"/>
+      <c r="K89" s="63"/>
+      <c r="L89" s="63"/>
+      <c r="M89" s="63"/>
+      <c r="N89" s="63"/>
+      <c r="O89" s="63"/>
+      <c r="P89" s="63"/>
+      <c r="Q89" s="63"/>
+      <c r="R89" s="63"/>
+      <c r="S89" s="63"/>
+      <c r="T89" s="63"/>
       <c r="U89" s="64"/>
     </row>
     <row r="90" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A90" s="80"/>
+      <c r="A90" s="68"/>
       <c r="B90" s="30" t="s">
         <v>131</v>
       </c>
@@ -4984,26 +4978,26 @@
         <v>26</v>
       </c>
       <c r="D90" s="83"/>
-      <c r="E90" s="84"/>
-      <c r="F90" s="84"/>
-      <c r="G90" s="84"/>
-      <c r="H90" s="84"/>
-      <c r="I90" s="84"/>
-      <c r="J90" s="84"/>
-      <c r="K90" s="84"/>
-      <c r="L90" s="84"/>
-      <c r="M90" s="84"/>
-      <c r="N90" s="84"/>
-      <c r="O90" s="84"/>
-      <c r="P90" s="84"/>
-      <c r="Q90" s="84"/>
-      <c r="R90" s="84"/>
-      <c r="S90" s="84"/>
-      <c r="T90" s="84"/>
+      <c r="E90" s="63"/>
+      <c r="F90" s="63"/>
+      <c r="G90" s="63"/>
+      <c r="H90" s="63"/>
+      <c r="I90" s="63"/>
+      <c r="J90" s="63"/>
+      <c r="K90" s="63"/>
+      <c r="L90" s="63"/>
+      <c r="M90" s="63"/>
+      <c r="N90" s="63"/>
+      <c r="O90" s="63"/>
+      <c r="P90" s="63"/>
+      <c r="Q90" s="63"/>
+      <c r="R90" s="63"/>
+      <c r="S90" s="63"/>
+      <c r="T90" s="63"/>
       <c r="U90" s="64"/>
     </row>
     <row r="91" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A91" s="80"/>
+      <c r="A91" s="68"/>
       <c r="B91" s="30" t="s">
         <v>132</v>
       </c>
@@ -5011,26 +5005,26 @@
         <v>32</v>
       </c>
       <c r="D91" s="83"/>
-      <c r="E91" s="84"/>
-      <c r="F91" s="84"/>
-      <c r="G91" s="84"/>
-      <c r="H91" s="84"/>
-      <c r="I91" s="84"/>
-      <c r="J91" s="84"/>
-      <c r="K91" s="84"/>
-      <c r="L91" s="84"/>
-      <c r="M91" s="84"/>
-      <c r="N91" s="84"/>
-      <c r="O91" s="84"/>
-      <c r="P91" s="84"/>
-      <c r="Q91" s="84"/>
-      <c r="R91" s="84"/>
-      <c r="S91" s="84"/>
-      <c r="T91" s="84"/>
+      <c r="E91" s="63"/>
+      <c r="F91" s="63"/>
+      <c r="G91" s="63"/>
+      <c r="H91" s="63"/>
+      <c r="I91" s="63"/>
+      <c r="J91" s="63"/>
+      <c r="K91" s="63"/>
+      <c r="L91" s="63"/>
+      <c r="M91" s="63"/>
+      <c r="N91" s="63"/>
+      <c r="O91" s="63"/>
+      <c r="P91" s="63"/>
+      <c r="Q91" s="63"/>
+      <c r="R91" s="63"/>
+      <c r="S91" s="63"/>
+      <c r="T91" s="63"/>
       <c r="U91" s="64"/>
     </row>
     <row r="92" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A92" s="80"/>
+      <c r="A92" s="68"/>
       <c r="B92" s="30" t="s">
         <v>133</v>
       </c>
@@ -5038,26 +5032,26 @@
         <v>37</v>
       </c>
       <c r="D92" s="83"/>
-      <c r="E92" s="84"/>
-      <c r="F92" s="84"/>
-      <c r="G92" s="84"/>
-      <c r="H92" s="84"/>
-      <c r="I92" s="84"/>
-      <c r="J92" s="84"/>
-      <c r="K92" s="84"/>
-      <c r="L92" s="84"/>
-      <c r="M92" s="84"/>
-      <c r="N92" s="84"/>
-      <c r="O92" s="84"/>
-      <c r="P92" s="84"/>
-      <c r="Q92" s="84"/>
-      <c r="R92" s="84"/>
-      <c r="S92" s="84"/>
-      <c r="T92" s="84"/>
+      <c r="E92" s="63"/>
+      <c r="F92" s="63"/>
+      <c r="G92" s="63"/>
+      <c r="H92" s="63"/>
+      <c r="I92" s="63"/>
+      <c r="J92" s="63"/>
+      <c r="K92" s="63"/>
+      <c r="L92" s="63"/>
+      <c r="M92" s="63"/>
+      <c r="N92" s="63"/>
+      <c r="O92" s="63"/>
+      <c r="P92" s="63"/>
+      <c r="Q92" s="63"/>
+      <c r="R92" s="63"/>
+      <c r="S92" s="63"/>
+      <c r="T92" s="63"/>
       <c r="U92" s="64"/>
     </row>
     <row r="93" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A93" s="80"/>
+      <c r="A93" s="68"/>
       <c r="B93" s="30" t="s">
         <v>134</v>
       </c>
@@ -5065,33 +5059,33 @@
         <v>40</v>
       </c>
       <c r="D93" s="83"/>
-      <c r="E93" s="84"/>
-      <c r="F93" s="84"/>
-      <c r="G93" s="84"/>
-      <c r="H93" s="84"/>
-      <c r="I93" s="84"/>
-      <c r="J93" s="84"/>
-      <c r="K93" s="84"/>
-      <c r="L93" s="84"/>
-      <c r="M93" s="84"/>
-      <c r="N93" s="84"/>
-      <c r="O93" s="84"/>
-      <c r="P93" s="84"/>
-      <c r="Q93" s="84"/>
-      <c r="R93" s="84"/>
-      <c r="S93" s="84"/>
-      <c r="T93" s="84"/>
+      <c r="E93" s="63"/>
+      <c r="F93" s="63"/>
+      <c r="G93" s="63"/>
+      <c r="H93" s="63"/>
+      <c r="I93" s="63"/>
+      <c r="J93" s="63"/>
+      <c r="K93" s="63"/>
+      <c r="L93" s="63"/>
+      <c r="M93" s="63"/>
+      <c r="N93" s="63"/>
+      <c r="O93" s="63"/>
+      <c r="P93" s="63"/>
+      <c r="Q93" s="63"/>
+      <c r="R93" s="63"/>
+      <c r="S93" s="63"/>
+      <c r="T93" s="63"/>
       <c r="U93" s="64"/>
     </row>
     <row r="94" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A94" s="81"/>
+      <c r="A94" s="69"/>
       <c r="B94" s="30" t="s">
         <v>135</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D94" s="85"/>
+      <c r="D94" s="84"/>
       <c r="E94" s="65"/>
       <c r="F94" s="65"/>
       <c r="G94" s="65"/>
@@ -5111,7 +5105,7 @@
       <c r="U94" s="66"/>
     </row>
     <row r="95" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A95" s="72">
+      <c r="A95" s="73">
         <v>14</v>
       </c>
       <c r="B95" s="28" t="s">
@@ -5144,7 +5138,7 @@
       <c r="U95" s="17"/>
     </row>
     <row r="96" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A96" s="73"/>
+      <c r="A96" s="74"/>
       <c r="B96" s="28" t="s">
         <v>138</v>
       </c>
@@ -5175,7 +5169,7 @@
       <c r="U96" s="17"/>
     </row>
     <row r="97" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A97" s="73"/>
+      <c r="A97" s="74"/>
       <c r="B97" s="28" t="s">
         <v>139</v>
       </c>
@@ -5206,7 +5200,7 @@
       <c r="U97" s="17"/>
     </row>
     <row r="98" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A98" s="73"/>
+      <c r="A98" s="74"/>
       <c r="B98" s="28" t="s">
         <v>140</v>
       </c>
@@ -5237,7 +5231,7 @@
       <c r="U98" s="17"/>
     </row>
     <row r="99" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A99" s="73"/>
+      <c r="A99" s="74"/>
       <c r="B99" s="28" t="s">
         <v>141</v>
       </c>
@@ -5268,7 +5262,7 @@
       <c r="U99" s="17"/>
     </row>
     <row r="100" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A100" s="73"/>
+      <c r="A100" s="74"/>
       <c r="B100" s="28" t="s">
         <v>142</v>
       </c>
@@ -5299,7 +5293,7 @@
       <c r="U100" s="17"/>
     </row>
     <row r="101" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A101" s="74"/>
+      <c r="A101" s="75"/>
       <c r="B101" s="28" t="s">
         <v>143</v>
       </c>
@@ -5330,7 +5324,7 @@
       <c r="U101" s="17"/>
     </row>
     <row r="102" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A102" s="79">
+      <c r="A102" s="67">
         <v>15</v>
       </c>
       <c r="B102" s="30" t="s">
@@ -5363,7 +5357,7 @@
       <c r="U102" s="6"/>
     </row>
     <row r="103" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A103" s="80"/>
+      <c r="A103" s="68"/>
       <c r="B103" s="30" t="s">
         <v>145</v>
       </c>
@@ -5394,7 +5388,7 @@
       <c r="U103" s="6"/>
     </row>
     <row r="104" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A104" s="80"/>
+      <c r="A104" s="68"/>
       <c r="B104" s="30" t="s">
         <v>146</v>
       </c>
@@ -5425,7 +5419,7 @@
       <c r="U104" s="6"/>
     </row>
     <row r="105" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A105" s="80"/>
+      <c r="A105" s="68"/>
       <c r="B105" s="30" t="s">
         <v>147</v>
       </c>
@@ -5456,7 +5450,7 @@
       <c r="U105" s="6"/>
     </row>
     <row r="106" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A106" s="80"/>
+      <c r="A106" s="68"/>
       <c r="B106" s="30" t="s">
         <v>148</v>
       </c>
@@ -5487,7 +5481,7 @@
       <c r="U106" s="6"/>
     </row>
     <row r="107" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A107" s="80"/>
+      <c r="A107" s="68"/>
       <c r="B107" s="30" t="s">
         <v>149</v>
       </c>
@@ -5518,7 +5512,7 @@
       <c r="U107" s="6"/>
     </row>
     <row r="108" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A108" s="81"/>
+      <c r="A108" s="69"/>
       <c r="B108" s="30" t="s">
         <v>150</v>
       </c>
@@ -5549,7 +5543,7 @@
       <c r="U108" s="6"/>
     </row>
     <row r="109" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A109" s="72">
+      <c r="A109" s="73">
         <v>16</v>
       </c>
       <c r="B109" s="28" t="s">
@@ -5582,7 +5576,7 @@
       <c r="U109" s="16"/>
     </row>
     <row r="110" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A110" s="73"/>
+      <c r="A110" s="74"/>
       <c r="B110" s="28" t="s">
         <v>152</v>
       </c>
@@ -5613,7 +5607,7 @@
       <c r="U110" s="16"/>
     </row>
     <row r="111" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A111" s="73"/>
+      <c r="A111" s="74"/>
       <c r="B111" s="28" t="s">
         <v>153</v>
       </c>
@@ -5644,7 +5638,7 @@
       <c r="U111" s="16"/>
     </row>
     <row r="112" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A112" s="73"/>
+      <c r="A112" s="74"/>
       <c r="B112" s="28" t="s">
         <v>154</v>
       </c>
@@ -5675,7 +5669,7 @@
       <c r="U112" s="16"/>
     </row>
     <row r="113" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A113" s="73"/>
+      <c r="A113" s="74"/>
       <c r="B113" s="28" t="s">
         <v>155</v>
       </c>
@@ -5706,7 +5700,7 @@
       <c r="U113" s="16"/>
     </row>
     <row r="114" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A114" s="73"/>
+      <c r="A114" s="74"/>
       <c r="B114" s="28" t="s">
         <v>156</v>
       </c>
@@ -5737,7 +5731,7 @@
       <c r="U114" s="16"/>
     </row>
     <row r="115" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A115" s="74"/>
+      <c r="A115" s="75"/>
       <c r="B115" s="28" t="s">
         <v>157</v>
       </c>
@@ -5768,7 +5762,7 @@
       <c r="U115" s="16"/>
     </row>
     <row r="116" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A116" s="79">
+      <c r="A116" s="67">
         <v>17</v>
       </c>
       <c r="B116" s="30" t="s">
@@ -5801,7 +5795,7 @@
       <c r="U116" s="6"/>
     </row>
     <row r="117" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A117" s="80"/>
+      <c r="A117" s="68"/>
       <c r="B117" s="30" t="s">
         <v>159</v>
       </c>
@@ -5832,7 +5826,7 @@
       <c r="U117" s="6"/>
     </row>
     <row r="118" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A118" s="80"/>
+      <c r="A118" s="68"/>
       <c r="B118" s="30" t="s">
         <v>160</v>
       </c>
@@ -5863,7 +5857,7 @@
       <c r="U118" s="6"/>
     </row>
     <row r="119" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A119" s="80"/>
+      <c r="A119" s="68"/>
       <c r="B119" s="30" t="s">
         <v>161</v>
       </c>
@@ -5894,7 +5888,7 @@
       <c r="U119" s="6"/>
     </row>
     <row r="120" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A120" s="80"/>
+      <c r="A120" s="68"/>
       <c r="B120" s="30" t="s">
         <v>162</v>
       </c>
@@ -5925,7 +5919,7 @@
       <c r="U120" s="6"/>
     </row>
     <row r="121" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A121" s="80"/>
+      <c r="A121" s="68"/>
       <c r="B121" s="30" t="s">
         <v>163</v>
       </c>
@@ -5956,7 +5950,7 @@
       <c r="U121" s="6"/>
     </row>
     <row r="122" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A122" s="81"/>
+      <c r="A122" s="69"/>
       <c r="B122" s="30" t="s">
         <v>164</v>
       </c>
@@ -5987,7 +5981,7 @@
       <c r="U122" s="6"/>
     </row>
     <row r="123" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A123" s="72">
+      <c r="A123" s="73">
         <v>18</v>
       </c>
       <c r="B123" s="28" t="s">
@@ -6020,7 +6014,7 @@
       <c r="U123" s="16"/>
     </row>
     <row r="124" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A124" s="73"/>
+      <c r="A124" s="74"/>
       <c r="B124" s="28" t="s">
         <v>166</v>
       </c>
@@ -6051,7 +6045,7 @@
       <c r="U124" s="16"/>
     </row>
     <row r="125" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A125" s="73"/>
+      <c r="A125" s="74"/>
       <c r="B125" s="28" t="s">
         <v>167</v>
       </c>
@@ -6082,7 +6076,7 @@
       <c r="U125" s="16"/>
     </row>
     <row r="126" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A126" s="73"/>
+      <c r="A126" s="74"/>
       <c r="B126" s="28" t="s">
         <v>168</v>
       </c>
@@ -6113,14 +6107,14 @@
       <c r="U126" s="16"/>
     </row>
     <row r="127" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A127" s="73"/>
+      <c r="A127" s="74"/>
       <c r="B127" s="27" t="s">
         <v>169</v>
       </c>
       <c r="C127" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="D127" s="86" t="s">
+      <c r="D127" s="81" t="s">
         <v>69</v>
       </c>
       <c r="E127" s="59"/>
@@ -6142,7 +6136,7 @@
       <c r="U127" s="60"/>
     </row>
     <row r="128" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A128" s="73"/>
+      <c r="A128" s="74"/>
       <c r="B128" s="28" t="s">
         <v>170</v>
       </c>
@@ -6173,7 +6167,7 @@
       <c r="U128" s="16"/>
     </row>
     <row r="129" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A129" s="74"/>
+      <c r="A129" s="75"/>
       <c r="B129" s="28" t="s">
         <v>171</v>
       </c>
@@ -6204,7 +6198,7 @@
       <c r="U129" s="16"/>
     </row>
     <row r="130" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A130" s="79">
+      <c r="A130" s="67">
         <v>19</v>
       </c>
       <c r="B130" s="30" t="s">
@@ -6237,7 +6231,7 @@
       <c r="U130" s="6"/>
     </row>
     <row r="131" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A131" s="80"/>
+      <c r="A131" s="68"/>
       <c r="B131" s="30" t="s">
         <v>173</v>
       </c>
@@ -6268,7 +6262,7 @@
       <c r="U131" s="6"/>
     </row>
     <row r="132" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A132" s="80"/>
+      <c r="A132" s="68"/>
       <c r="B132" s="30" t="s">
         <v>174</v>
       </c>
@@ -6299,7 +6293,7 @@
       <c r="U132" s="6"/>
     </row>
     <row r="133" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A133" s="80"/>
+      <c r="A133" s="68"/>
       <c r="B133" s="30" t="s">
         <v>175</v>
       </c>
@@ -6330,7 +6324,7 @@
       <c r="U133" s="6"/>
     </row>
     <row r="134" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A134" s="80"/>
+      <c r="A134" s="68"/>
       <c r="B134" s="30" t="s">
         <v>176</v>
       </c>
@@ -6361,7 +6355,7 @@
       <c r="U134" s="6"/>
     </row>
     <row r="135" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A135" s="80"/>
+      <c r="A135" s="68"/>
       <c r="B135" s="30" t="s">
         <v>177</v>
       </c>
@@ -6392,7 +6386,7 @@
       <c r="U135" s="6"/>
     </row>
     <row r="136" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A136" s="81"/>
+      <c r="A136" s="69"/>
       <c r="B136" s="30" t="s">
         <v>178</v>
       </c>
@@ -6438,6 +6432,7 @@
     <row r="150" ht="20.25"/>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="A74:A80"/>
     <mergeCell ref="A123:A129"/>
     <mergeCell ref="D127:U127"/>
     <mergeCell ref="A130:A136"/>
@@ -6448,18 +6443,16 @@
     <mergeCell ref="A109:A115"/>
     <mergeCell ref="A116:A122"/>
     <mergeCell ref="A81:A87"/>
+    <mergeCell ref="M2:O2"/>
     <mergeCell ref="A46:A52"/>
     <mergeCell ref="A53:A59"/>
     <mergeCell ref="A60:A66"/>
     <mergeCell ref="A67:A73"/>
-    <mergeCell ref="A74:A80"/>
-    <mergeCell ref="J2:L2"/>
     <mergeCell ref="A4:A10"/>
     <mergeCell ref="A11:A17"/>
     <mergeCell ref="A18:A24"/>
     <mergeCell ref="A25:A31"/>
     <mergeCell ref="D29:U31"/>
-    <mergeCell ref="M2:O2"/>
     <mergeCell ref="A32:A38"/>
     <mergeCell ref="D35:U41"/>
     <mergeCell ref="A39:A45"/>
@@ -6475,6 +6468,7 @@
     <mergeCell ref="B2:C3"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
+    <mergeCell ref="J2:L2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6517,46 +6511,46 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="53" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="55" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="56"/>
-      <c r="D2" s="45" t="s">
+      <c r="D2" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45" t="s">
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45" t="s">
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="45" t="s">
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="45"/>
-      <c r="O2" s="45"/>
-      <c r="P2" s="45" t="s">
+      <c r="N2" s="53"/>
+      <c r="O2" s="53"/>
+      <c r="P2" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="45"/>
-      <c r="R2" s="45"/>
-      <c r="S2" s="45" t="s">
+      <c r="Q2" s="53"/>
+      <c r="R2" s="53"/>
+      <c r="S2" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="T2" s="45"/>
-      <c r="U2" s="45"/>
+      <c r="T2" s="53"/>
+      <c r="U2" s="53"/>
     </row>
     <row r="3" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="45"/>
+      <c r="A3" s="53"/>
       <c r="B3" s="57"/>
       <c r="C3" s="58"/>
       <c r="D3" s="54" t="s">
@@ -6564,34 +6558,34 @@
       </c>
       <c r="E3" s="54"/>
       <c r="F3" s="54"/>
-      <c r="G3" s="45" t="s">
+      <c r="G3" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45" t="s">
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="45"/>
-      <c r="L3" s="45"/>
-      <c r="M3" s="45" t="s">
+      <c r="K3" s="53"/>
+      <c r="L3" s="53"/>
+      <c r="M3" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="45"/>
-      <c r="O3" s="45"/>
-      <c r="P3" s="45" t="s">
+      <c r="N3" s="53"/>
+      <c r="O3" s="53"/>
+      <c r="P3" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="45"/>
-      <c r="R3" s="45"/>
-      <c r="S3" s="45" t="s">
+      <c r="Q3" s="53"/>
+      <c r="R3" s="53"/>
+      <c r="S3" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="45"/>
-      <c r="U3" s="45"/>
+      <c r="T3" s="53"/>
+      <c r="U3" s="53"/>
     </row>
     <row r="4" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="46">
+      <c r="A4" s="45">
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -6631,7 +6625,7 @@
       </c>
     </row>
     <row r="5" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A5" s="46"/>
+      <c r="A5" s="45"/>
       <c r="B5" s="2" t="s">
         <v>23</v>
       </c>
@@ -6695,7 +6689,7 @@
       </c>
     </row>
     <row r="6" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="46"/>
+      <c r="A6" s="45"/>
       <c r="B6" s="2" t="s">
         <v>25</v>
       </c>
@@ -6739,7 +6733,7 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="46"/>
+      <c r="A7" s="45"/>
       <c r="B7" s="2" t="s">
         <v>31</v>
       </c>
@@ -6803,7 +6797,7 @@
       </c>
     </row>
     <row r="8" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A8" s="46"/>
+      <c r="A8" s="45"/>
       <c r="B8" s="2" t="s">
         <v>36</v>
       </c>
@@ -6865,7 +6859,7 @@
       </c>
     </row>
     <row r="9" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="46"/>
+      <c r="A9" s="45"/>
       <c r="B9" s="2" t="s">
         <v>39</v>
       </c>
@@ -6909,7 +6903,7 @@
       </c>
     </row>
     <row r="10" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A10" s="46"/>
+      <c r="A10" s="45"/>
       <c r="B10" s="2" t="s">
         <v>43</v>
       </c>
@@ -6951,7 +6945,7 @@
       </c>
     </row>
     <row r="11" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A11" s="53">
+      <c r="A11" s="52">
         <v>2</v>
       </c>
       <c r="B11" s="13" t="s">
@@ -7017,7 +7011,7 @@
       </c>
     </row>
     <row r="12" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="53"/>
+      <c r="A12" s="52"/>
       <c r="B12" s="13" t="s">
         <v>47</v>
       </c>
@@ -7079,7 +7073,7 @@
       </c>
     </row>
     <row r="13" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="53"/>
+      <c r="A13" s="52"/>
       <c r="B13" s="13" t="s">
         <v>49</v>
       </c>
@@ -7131,7 +7125,7 @@
       <c r="AA13" s="3"/>
     </row>
     <row r="14" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="53"/>
+      <c r="A14" s="52"/>
       <c r="B14" s="13" t="s">
         <v>50</v>
       </c>
@@ -7195,7 +7189,7 @@
       <c r="AA14" s="3"/>
     </row>
     <row r="15" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="53"/>
+      <c r="A15" s="52"/>
       <c r="B15" s="13" t="s">
         <v>54</v>
       </c>
@@ -7247,7 +7241,7 @@
       <c r="AA15" s="3"/>
     </row>
     <row r="16" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="53"/>
+      <c r="A16" s="52"/>
       <c r="B16" s="13" t="s">
         <v>55</v>
       </c>
@@ -7279,7 +7273,7 @@
       <c r="AA16" s="3"/>
     </row>
     <row r="17" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A17" s="53"/>
+      <c r="A17" s="52"/>
       <c r="B17" s="13" t="s">
         <v>56</v>
       </c>
@@ -7306,7 +7300,7 @@
       <c r="U17" s="17"/>
     </row>
     <row r="18" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A18" s="46">
+      <c r="A18" s="45">
         <v>3</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -7355,7 +7349,7 @@
       <c r="U18" s="6"/>
     </row>
     <row r="19" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A19" s="46"/>
+      <c r="A19" s="45"/>
       <c r="B19" s="2" t="s">
         <v>58</v>
       </c>
@@ -7402,7 +7396,7 @@
       <c r="U19" s="6"/>
     </row>
     <row r="20" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A20" s="46"/>
+      <c r="A20" s="45"/>
       <c r="B20" s="2" t="s">
         <v>59</v>
       </c>
@@ -7449,7 +7443,7 @@
       <c r="U20" s="6"/>
     </row>
     <row r="21" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A21" s="46"/>
+      <c r="A21" s="45"/>
       <c r="B21" s="2" t="s">
         <v>60</v>
       </c>
@@ -7508,7 +7502,7 @@
       </c>
     </row>
     <row r="22" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A22" s="46"/>
+      <c r="A22" s="45"/>
       <c r="B22" s="2" t="s">
         <v>61</v>
       </c>
@@ -7555,7 +7549,7 @@
       <c r="U22" s="6"/>
     </row>
     <row r="23" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A23" s="46"/>
+      <c r="A23" s="45"/>
       <c r="B23" s="2" t="s">
         <v>62</v>
       </c>
@@ -7582,7 +7576,7 @@
       <c r="U23" s="6"/>
     </row>
     <row r="24" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A24" s="46"/>
+      <c r="A24" s="45"/>
       <c r="B24" s="18" t="s">
         <v>63</v>
       </c>
@@ -7621,7 +7615,7 @@
       <c r="U24" s="22"/>
     </row>
     <row r="25" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A25" s="53">
+      <c r="A25" s="52">
         <v>4</v>
       </c>
       <c r="B25" s="13" t="s">
@@ -7652,7 +7646,7 @@
       <c r="U25" s="17"/>
     </row>
     <row r="26" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A26" s="53"/>
+      <c r="A26" s="52"/>
       <c r="B26" s="13" t="s">
         <v>65</v>
       </c>
@@ -7699,7 +7693,7 @@
       <c r="U26" s="17"/>
     </row>
     <row r="27" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A27" s="53"/>
+      <c r="A27" s="52"/>
       <c r="B27" s="13" t="s">
         <v>66</v>
       </c>
@@ -7746,7 +7740,7 @@
       <c r="U27" s="17"/>
     </row>
     <row r="28" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A28" s="53"/>
+      <c r="A28" s="52"/>
       <c r="B28" s="13" t="s">
         <v>67</v>
       </c>
@@ -7793,90 +7787,90 @@
       <c r="U28" s="17"/>
     </row>
     <row r="29" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A29" s="53"/>
+      <c r="A29" s="52"/>
       <c r="B29" s="25" t="s">
         <v>68</v>
       </c>
       <c r="C29" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="D29" s="47" t="s">
+      <c r="D29" s="46" t="s">
         <v>69</v>
       </c>
-      <c r="E29" s="47"/>
-      <c r="F29" s="47"/>
-      <c r="G29" s="47"/>
-      <c r="H29" s="47"/>
-      <c r="I29" s="47"/>
-      <c r="J29" s="47"/>
-      <c r="K29" s="47"/>
-      <c r="L29" s="47"/>
-      <c r="M29" s="47"/>
-      <c r="N29" s="47"/>
-      <c r="O29" s="47"/>
-      <c r="P29" s="47"/>
-      <c r="Q29" s="47"/>
-      <c r="R29" s="47"/>
-      <c r="S29" s="47"/>
-      <c r="T29" s="47"/>
-      <c r="U29" s="48"/>
+      <c r="E29" s="46"/>
+      <c r="F29" s="46"/>
+      <c r="G29" s="46"/>
+      <c r="H29" s="46"/>
+      <c r="I29" s="46"/>
+      <c r="J29" s="46"/>
+      <c r="K29" s="46"/>
+      <c r="L29" s="46"/>
+      <c r="M29" s="46"/>
+      <c r="N29" s="46"/>
+      <c r="O29" s="46"/>
+      <c r="P29" s="46"/>
+      <c r="Q29" s="46"/>
+      <c r="R29" s="46"/>
+      <c r="S29" s="46"/>
+      <c r="T29" s="46"/>
+      <c r="U29" s="47"/>
     </row>
     <row r="30" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A30" s="53"/>
+      <c r="A30" s="52"/>
       <c r="B30" s="25" t="s">
         <v>70</v>
       </c>
       <c r="C30" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="D30" s="49"/>
-      <c r="E30" s="49"/>
-      <c r="F30" s="49"/>
-      <c r="G30" s="49"/>
-      <c r="H30" s="49"/>
-      <c r="I30" s="49"/>
-      <c r="J30" s="49"/>
-      <c r="K30" s="49"/>
-      <c r="L30" s="49"/>
-      <c r="M30" s="49"/>
-      <c r="N30" s="49"/>
-      <c r="O30" s="49"/>
-      <c r="P30" s="49"/>
-      <c r="Q30" s="49"/>
-      <c r="R30" s="49"/>
-      <c r="S30" s="49"/>
-      <c r="T30" s="49"/>
-      <c r="U30" s="50"/>
+      <c r="D30" s="48"/>
+      <c r="E30" s="48"/>
+      <c r="F30" s="48"/>
+      <c r="G30" s="48"/>
+      <c r="H30" s="48"/>
+      <c r="I30" s="48"/>
+      <c r="J30" s="48"/>
+      <c r="K30" s="48"/>
+      <c r="L30" s="48"/>
+      <c r="M30" s="48"/>
+      <c r="N30" s="48"/>
+      <c r="O30" s="48"/>
+      <c r="P30" s="48"/>
+      <c r="Q30" s="48"/>
+      <c r="R30" s="48"/>
+      <c r="S30" s="48"/>
+      <c r="T30" s="48"/>
+      <c r="U30" s="49"/>
     </row>
     <row r="31" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A31" s="53"/>
+      <c r="A31" s="52"/>
       <c r="B31" s="25" t="s">
         <v>71</v>
       </c>
       <c r="C31" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="D31" s="51"/>
-      <c r="E31" s="51"/>
-      <c r="F31" s="51"/>
-      <c r="G31" s="51"/>
-      <c r="H31" s="51"/>
-      <c r="I31" s="51"/>
-      <c r="J31" s="51"/>
-      <c r="K31" s="51"/>
-      <c r="L31" s="51"/>
-      <c r="M31" s="51"/>
-      <c r="N31" s="51"/>
-      <c r="O31" s="51"/>
-      <c r="P31" s="51"/>
-      <c r="Q31" s="51"/>
-      <c r="R31" s="51"/>
-      <c r="S31" s="51"/>
-      <c r="T31" s="51"/>
-      <c r="U31" s="52"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="50"/>
+      <c r="F31" s="50"/>
+      <c r="G31" s="50"/>
+      <c r="H31" s="50"/>
+      <c r="I31" s="50"/>
+      <c r="J31" s="50"/>
+      <c r="K31" s="50"/>
+      <c r="L31" s="50"/>
+      <c r="M31" s="50"/>
+      <c r="N31" s="50"/>
+      <c r="O31" s="50"/>
+      <c r="P31" s="50"/>
+      <c r="Q31" s="50"/>
+      <c r="R31" s="50"/>
+      <c r="S31" s="50"/>
+      <c r="T31" s="50"/>
+      <c r="U31" s="51"/>
     </row>
     <row r="32" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A32" s="46">
+      <c r="A32" s="45">
         <v>5</v>
       </c>
       <c r="B32" s="2" t="s">
@@ -7907,7 +7901,7 @@
       <c r="U32" s="6"/>
     </row>
     <row r="33" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A33" s="46"/>
+      <c r="A33" s="45"/>
       <c r="B33" s="2" t="s">
         <v>73</v>
       </c>
@@ -7954,7 +7948,7 @@
       <c r="U33" s="6"/>
     </row>
     <row r="34" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A34" s="46"/>
+      <c r="A34" s="45"/>
       <c r="B34" s="2" t="s">
         <v>74</v>
       </c>
@@ -8001,117 +7995,117 @@
       <c r="U34" s="6"/>
     </row>
     <row r="35" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A35" s="46"/>
+      <c r="A35" s="45"/>
       <c r="B35" s="27" t="s">
         <v>75</v>
       </c>
       <c r="C35" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="D35" s="47" t="s">
+      <c r="D35" s="46" t="s">
         <v>69</v>
       </c>
-      <c r="E35" s="47"/>
-      <c r="F35" s="47"/>
-      <c r="G35" s="47"/>
-      <c r="H35" s="47"/>
-      <c r="I35" s="47"/>
-      <c r="J35" s="47"/>
-      <c r="K35" s="47"/>
-      <c r="L35" s="47"/>
-      <c r="M35" s="47"/>
-      <c r="N35" s="47"/>
-      <c r="O35" s="47"/>
-      <c r="P35" s="47"/>
-      <c r="Q35" s="47"/>
-      <c r="R35" s="47"/>
-      <c r="S35" s="47"/>
-      <c r="T35" s="47"/>
-      <c r="U35" s="48"/>
+      <c r="E35" s="46"/>
+      <c r="F35" s="46"/>
+      <c r="G35" s="46"/>
+      <c r="H35" s="46"/>
+      <c r="I35" s="46"/>
+      <c r="J35" s="46"/>
+      <c r="K35" s="46"/>
+      <c r="L35" s="46"/>
+      <c r="M35" s="46"/>
+      <c r="N35" s="46"/>
+      <c r="O35" s="46"/>
+      <c r="P35" s="46"/>
+      <c r="Q35" s="46"/>
+      <c r="R35" s="46"/>
+      <c r="S35" s="46"/>
+      <c r="T35" s="46"/>
+      <c r="U35" s="47"/>
     </row>
     <row r="36" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A36" s="46"/>
+      <c r="A36" s="45"/>
       <c r="B36" s="27" t="s">
         <v>76</v>
       </c>
       <c r="C36" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="D36" s="49"/>
-      <c r="E36" s="49"/>
-      <c r="F36" s="49"/>
-      <c r="G36" s="49"/>
-      <c r="H36" s="49"/>
-      <c r="I36" s="49"/>
-      <c r="J36" s="49"/>
-      <c r="K36" s="49"/>
-      <c r="L36" s="49"/>
-      <c r="M36" s="49"/>
-      <c r="N36" s="49"/>
-      <c r="O36" s="49"/>
-      <c r="P36" s="49"/>
-      <c r="Q36" s="49"/>
-      <c r="R36" s="49"/>
-      <c r="S36" s="49"/>
-      <c r="T36" s="49"/>
-      <c r="U36" s="50"/>
+      <c r="D36" s="48"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="48"/>
+      <c r="H36" s="48"/>
+      <c r="I36" s="48"/>
+      <c r="J36" s="48"/>
+      <c r="K36" s="48"/>
+      <c r="L36" s="48"/>
+      <c r="M36" s="48"/>
+      <c r="N36" s="48"/>
+      <c r="O36" s="48"/>
+      <c r="P36" s="48"/>
+      <c r="Q36" s="48"/>
+      <c r="R36" s="48"/>
+      <c r="S36" s="48"/>
+      <c r="T36" s="48"/>
+      <c r="U36" s="49"/>
     </row>
     <row r="37" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A37" s="46"/>
+      <c r="A37" s="45"/>
       <c r="B37" s="27" t="s">
         <v>77</v>
       </c>
       <c r="C37" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="D37" s="49"/>
-      <c r="E37" s="49"/>
-      <c r="F37" s="49"/>
-      <c r="G37" s="49"/>
-      <c r="H37" s="49"/>
-      <c r="I37" s="49"/>
-      <c r="J37" s="49"/>
-      <c r="K37" s="49"/>
-      <c r="L37" s="49"/>
-      <c r="M37" s="49"/>
-      <c r="N37" s="49"/>
-      <c r="O37" s="49"/>
-      <c r="P37" s="49"/>
-      <c r="Q37" s="49"/>
-      <c r="R37" s="49"/>
-      <c r="S37" s="49"/>
-      <c r="T37" s="49"/>
-      <c r="U37" s="50"/>
+      <c r="D37" s="48"/>
+      <c r="E37" s="48"/>
+      <c r="F37" s="48"/>
+      <c r="G37" s="48"/>
+      <c r="H37" s="48"/>
+      <c r="I37" s="48"/>
+      <c r="J37" s="48"/>
+      <c r="K37" s="48"/>
+      <c r="L37" s="48"/>
+      <c r="M37" s="48"/>
+      <c r="N37" s="48"/>
+      <c r="O37" s="48"/>
+      <c r="P37" s="48"/>
+      <c r="Q37" s="48"/>
+      <c r="R37" s="48"/>
+      <c r="S37" s="48"/>
+      <c r="T37" s="48"/>
+      <c r="U37" s="49"/>
     </row>
     <row r="38" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A38" s="46"/>
+      <c r="A38" s="45"/>
       <c r="B38" s="27" t="s">
         <v>78</v>
       </c>
       <c r="C38" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="D38" s="49"/>
-      <c r="E38" s="49"/>
-      <c r="F38" s="49"/>
-      <c r="G38" s="49"/>
-      <c r="H38" s="49"/>
-      <c r="I38" s="49"/>
-      <c r="J38" s="49"/>
-      <c r="K38" s="49"/>
-      <c r="L38" s="49"/>
-      <c r="M38" s="49"/>
-      <c r="N38" s="49"/>
-      <c r="O38" s="49"/>
-      <c r="P38" s="49"/>
-      <c r="Q38" s="49"/>
-      <c r="R38" s="49"/>
-      <c r="S38" s="49"/>
-      <c r="T38" s="49"/>
-      <c r="U38" s="50"/>
+      <c r="D38" s="48"/>
+      <c r="E38" s="48"/>
+      <c r="F38" s="48"/>
+      <c r="G38" s="48"/>
+      <c r="H38" s="48"/>
+      <c r="I38" s="48"/>
+      <c r="J38" s="48"/>
+      <c r="K38" s="48"/>
+      <c r="L38" s="48"/>
+      <c r="M38" s="48"/>
+      <c r="N38" s="48"/>
+      <c r="O38" s="48"/>
+      <c r="P38" s="48"/>
+      <c r="Q38" s="48"/>
+      <c r="R38" s="48"/>
+      <c r="S38" s="48"/>
+      <c r="T38" s="48"/>
+      <c r="U38" s="49"/>
     </row>
     <row r="39" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A39" s="53">
+      <c r="A39" s="52">
         <v>6</v>
       </c>
       <c r="B39" s="27" t="s">
@@ -8120,81 +8114,81 @@
       <c r="C39" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="49"/>
-      <c r="E39" s="49"/>
-      <c r="F39" s="49"/>
-      <c r="G39" s="49"/>
-      <c r="H39" s="49"/>
-      <c r="I39" s="49"/>
-      <c r="J39" s="49"/>
-      <c r="K39" s="49"/>
-      <c r="L39" s="49"/>
-      <c r="M39" s="49"/>
-      <c r="N39" s="49"/>
-      <c r="O39" s="49"/>
-      <c r="P39" s="49"/>
-      <c r="Q39" s="49"/>
-      <c r="R39" s="49"/>
-      <c r="S39" s="49"/>
-      <c r="T39" s="49"/>
-      <c r="U39" s="50"/>
+      <c r="D39" s="48"/>
+      <c r="E39" s="48"/>
+      <c r="F39" s="48"/>
+      <c r="G39" s="48"/>
+      <c r="H39" s="48"/>
+      <c r="I39" s="48"/>
+      <c r="J39" s="48"/>
+      <c r="K39" s="48"/>
+      <c r="L39" s="48"/>
+      <c r="M39" s="48"/>
+      <c r="N39" s="48"/>
+      <c r="O39" s="48"/>
+      <c r="P39" s="48"/>
+      <c r="Q39" s="48"/>
+      <c r="R39" s="48"/>
+      <c r="S39" s="48"/>
+      <c r="T39" s="48"/>
+      <c r="U39" s="49"/>
     </row>
     <row r="40" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A40" s="53"/>
+      <c r="A40" s="52"/>
       <c r="B40" s="27" t="s">
         <v>80</v>
       </c>
       <c r="C40" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="D40" s="49"/>
-      <c r="E40" s="49"/>
-      <c r="F40" s="49"/>
-      <c r="G40" s="49"/>
-      <c r="H40" s="49"/>
-      <c r="I40" s="49"/>
-      <c r="J40" s="49"/>
-      <c r="K40" s="49"/>
-      <c r="L40" s="49"/>
-      <c r="M40" s="49"/>
-      <c r="N40" s="49"/>
-      <c r="O40" s="49"/>
-      <c r="P40" s="49"/>
-      <c r="Q40" s="49"/>
-      <c r="R40" s="49"/>
-      <c r="S40" s="49"/>
-      <c r="T40" s="49"/>
-      <c r="U40" s="50"/>
+      <c r="D40" s="48"/>
+      <c r="E40" s="48"/>
+      <c r="F40" s="48"/>
+      <c r="G40" s="48"/>
+      <c r="H40" s="48"/>
+      <c r="I40" s="48"/>
+      <c r="J40" s="48"/>
+      <c r="K40" s="48"/>
+      <c r="L40" s="48"/>
+      <c r="M40" s="48"/>
+      <c r="N40" s="48"/>
+      <c r="O40" s="48"/>
+      <c r="P40" s="48"/>
+      <c r="Q40" s="48"/>
+      <c r="R40" s="48"/>
+      <c r="S40" s="48"/>
+      <c r="T40" s="48"/>
+      <c r="U40" s="49"/>
     </row>
     <row r="41" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A41" s="53"/>
+      <c r="A41" s="52"/>
       <c r="B41" s="27" t="s">
         <v>81</v>
       </c>
       <c r="C41" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="D41" s="51"/>
-      <c r="E41" s="51"/>
-      <c r="F41" s="51"/>
-      <c r="G41" s="51"/>
-      <c r="H41" s="51"/>
-      <c r="I41" s="51"/>
-      <c r="J41" s="51"/>
-      <c r="K41" s="51"/>
-      <c r="L41" s="51"/>
-      <c r="M41" s="51"/>
-      <c r="N41" s="51"/>
-      <c r="O41" s="51"/>
-      <c r="P41" s="51"/>
-      <c r="Q41" s="51"/>
-      <c r="R41" s="51"/>
-      <c r="S41" s="51"/>
-      <c r="T41" s="51"/>
-      <c r="U41" s="52"/>
+      <c r="D41" s="50"/>
+      <c r="E41" s="50"/>
+      <c r="F41" s="50"/>
+      <c r="G41" s="50"/>
+      <c r="H41" s="50"/>
+      <c r="I41" s="50"/>
+      <c r="J41" s="50"/>
+      <c r="K41" s="50"/>
+      <c r="L41" s="50"/>
+      <c r="M41" s="50"/>
+      <c r="N41" s="50"/>
+      <c r="O41" s="50"/>
+      <c r="P41" s="50"/>
+      <c r="Q41" s="50"/>
+      <c r="R41" s="50"/>
+      <c r="S41" s="50"/>
+      <c r="T41" s="50"/>
+      <c r="U41" s="51"/>
     </row>
     <row r="42" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A42" s="53"/>
+      <c r="A42" s="52"/>
       <c r="B42" s="28" t="s">
         <v>82</v>
       </c>
@@ -8253,7 +8247,7 @@
       </c>
     </row>
     <row r="43" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A43" s="53"/>
+      <c r="A43" s="52"/>
       <c r="B43" s="28" t="s">
         <v>83</v>
       </c>
@@ -8300,7 +8294,7 @@
       <c r="U43" s="17"/>
     </row>
     <row r="44" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A44" s="53"/>
+      <c r="A44" s="52"/>
       <c r="B44" s="29" t="s">
         <v>84</v>
       </c>
@@ -8327,7 +8321,7 @@
       <c r="U44" s="22"/>
     </row>
     <row r="45" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A45" s="53"/>
+      <c r="A45" s="52"/>
       <c r="B45" s="28" t="s">
         <v>85</v>
       </c>
@@ -8354,7 +8348,7 @@
       <c r="U45" s="17"/>
     </row>
     <row r="46" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A46" s="46">
+      <c r="A46" s="45">
         <v>7</v>
       </c>
       <c r="B46" s="30" t="s">
@@ -8403,7 +8397,7 @@
       <c r="U46" s="6"/>
     </row>
     <row r="47" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A47" s="46"/>
+      <c r="A47" s="45"/>
       <c r="B47" s="30" t="s">
         <v>87</v>
       </c>
@@ -8450,7 +8444,7 @@
       <c r="U47" s="6"/>
     </row>
     <row r="48" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A48" s="46"/>
+      <c r="A48" s="45"/>
       <c r="B48" s="30" t="s">
         <v>88</v>
       </c>
@@ -8497,7 +8491,7 @@
       <c r="U48" s="6"/>
     </row>
     <row r="49" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A49" s="46"/>
+      <c r="A49" s="45"/>
       <c r="B49" s="30" t="s">
         <v>89</v>
       </c>
@@ -8544,7 +8538,7 @@
       <c r="U49" s="6"/>
     </row>
     <row r="50" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A50" s="46"/>
+      <c r="A50" s="45"/>
       <c r="B50" s="30" t="s">
         <v>90</v>
       </c>
@@ -8591,7 +8585,7 @@
       <c r="U50" s="6"/>
     </row>
     <row r="51" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A51" s="46"/>
+      <c r="A51" s="45"/>
       <c r="B51" s="30" t="s">
         <v>91</v>
       </c>
@@ -8601,15 +8595,8 @@
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
       <c r="F51" s="5"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="4"/>
       <c r="I51" s="41"/>
-      <c r="J51" s="2"/>
-      <c r="K51" s="4"/>
       <c r="L51" s="6"/>
-      <c r="M51" s="2"/>
-      <c r="N51" s="4"/>
-      <c r="O51" s="6"/>
       <c r="P51" s="2"/>
       <c r="Q51" s="4"/>
       <c r="R51" s="6"/>
@@ -8618,7 +8605,7 @@
       <c r="U51" s="6"/>
     </row>
     <row r="52" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A52" s="46"/>
+      <c r="A52" s="45"/>
       <c r="B52" s="30" t="s">
         <v>92</v>
       </c>
@@ -8645,7 +8632,7 @@
       <c r="U52" s="6"/>
     </row>
     <row r="53" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A53" s="53">
+      <c r="A53" s="52">
         <v>8</v>
       </c>
       <c r="B53" s="28" t="s">
@@ -8694,7 +8681,7 @@
       <c r="U53" s="17"/>
     </row>
     <row r="54" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A54" s="53"/>
+      <c r="A54" s="52"/>
       <c r="B54" s="28" t="s">
         <v>94</v>
       </c>
@@ -8741,7 +8728,7 @@
       <c r="U54" s="17"/>
     </row>
     <row r="55" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A55" s="53"/>
+      <c r="A55" s="52"/>
       <c r="B55" s="28" t="s">
         <v>95</v>
       </c>
@@ -8788,7 +8775,7 @@
       <c r="U55" s="17"/>
     </row>
     <row r="56" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A56" s="53"/>
+      <c r="A56" s="52"/>
       <c r="B56" s="28" t="s">
         <v>96</v>
       </c>
@@ -8847,7 +8834,7 @@
       </c>
     </row>
     <row r="57" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A57" s="53"/>
+      <c r="A57" s="52"/>
       <c r="B57" s="28" t="s">
         <v>97</v>
       </c>
@@ -8894,7 +8881,7 @@
       <c r="U57" s="17"/>
     </row>
     <row r="58" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A58" s="53"/>
+      <c r="A58" s="52"/>
       <c r="B58" s="28" t="s">
         <v>98</v>
       </c>
@@ -8921,7 +8908,7 @@
       <c r="U58" s="17"/>
     </row>
     <row r="59" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A59" s="53"/>
+      <c r="A59" s="52"/>
       <c r="B59" s="28" t="s">
         <v>99</v>
       </c>
@@ -8948,7 +8935,7 @@
       <c r="U59" s="17"/>
     </row>
     <row r="60" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A60" s="46">
+      <c r="A60" s="45">
         <v>9</v>
       </c>
       <c r="B60" s="30" t="s">
@@ -8979,7 +8966,7 @@
       <c r="U60" s="6"/>
     </row>
     <row r="61" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A61" s="46"/>
+      <c r="A61" s="45"/>
       <c r="B61" s="30" t="s">
         <v>101</v>
       </c>
@@ -9026,7 +9013,7 @@
       <c r="U61" s="6"/>
     </row>
     <row r="62" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A62" s="46"/>
+      <c r="A62" s="45"/>
       <c r="B62" s="30" t="s">
         <v>102</v>
       </c>
@@ -9055,7 +9042,7 @@
       <c r="U62" s="6"/>
     </row>
     <row r="63" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A63" s="46"/>
+      <c r="A63" s="45"/>
       <c r="B63" s="30" t="s">
         <v>103</v>
       </c>
@@ -9114,7 +9101,7 @@
       </c>
     </row>
     <row r="64" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A64" s="46"/>
+      <c r="A64" s="45"/>
       <c r="B64" s="30" t="s">
         <v>104</v>
       </c>
@@ -9161,7 +9148,7 @@
       <c r="U64" s="5"/>
     </row>
     <row r="65" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A65" s="46"/>
+      <c r="A65" s="45"/>
       <c r="B65" s="30" t="s">
         <v>105</v>
       </c>
@@ -9188,7 +9175,7 @@
       <c r="U65" s="5"/>
     </row>
     <row r="66" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A66" s="46"/>
+      <c r="A66" s="45"/>
       <c r="B66" s="30" t="s">
         <v>106</v>
       </c>
@@ -9215,7 +9202,7 @@
       <c r="U66" s="5"/>
     </row>
     <row r="67" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A67" s="53">
+      <c r="A67" s="52">
         <v>10</v>
       </c>
       <c r="B67" s="28" t="s">
@@ -9246,7 +9233,7 @@
       <c r="U67" s="16"/>
     </row>
     <row r="68" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A68" s="53"/>
+      <c r="A68" s="52"/>
       <c r="B68" s="28" t="s">
         <v>108</v>
       </c>
@@ -9293,7 +9280,7 @@
       <c r="U68" s="16"/>
     </row>
     <row r="69" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A69" s="53"/>
+      <c r="A69" s="52"/>
       <c r="B69" s="28" t="s">
         <v>109</v>
       </c>
@@ -9322,7 +9309,7 @@
       <c r="U69" s="16"/>
     </row>
     <row r="70" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A70" s="53"/>
+      <c r="A70" s="52"/>
       <c r="B70" s="28" t="s">
         <v>110</v>
       </c>
@@ -9363,7 +9350,7 @@
       </c>
     </row>
     <row r="71" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A71" s="53"/>
+      <c r="A71" s="52"/>
       <c r="B71" s="28" t="s">
         <v>111</v>
       </c>
@@ -9410,7 +9397,7 @@
       <c r="U71" s="16"/>
     </row>
     <row r="72" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A72" s="53"/>
+      <c r="A72" s="52"/>
       <c r="B72" s="28" t="s">
         <v>112</v>
       </c>
@@ -9437,7 +9424,7 @@
       <c r="U72" s="16"/>
     </row>
     <row r="73" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A73" s="53"/>
+      <c r="A73" s="52"/>
       <c r="B73" s="28" t="s">
         <v>113</v>
       </c>
@@ -9464,7 +9451,7 @@
       <c r="U73" s="16"/>
     </row>
     <row r="74" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A74" s="46">
+      <c r="A74" s="45">
         <v>11</v>
       </c>
       <c r="B74" s="30" t="s">
@@ -9495,7 +9482,7 @@
       <c r="U74" s="5"/>
     </row>
     <row r="75" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A75" s="46"/>
+      <c r="A75" s="45"/>
       <c r="B75" s="30" t="s">
         <v>115</v>
       </c>
@@ -9542,7 +9529,7 @@
       <c r="U75" s="5"/>
     </row>
     <row r="76" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A76" s="46"/>
+      <c r="A76" s="45"/>
       <c r="B76" s="30" t="s">
         <v>116</v>
       </c>
@@ -9571,7 +9558,7 @@
       <c r="U76" s="5"/>
     </row>
     <row r="77" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A77" s="46"/>
+      <c r="A77" s="45"/>
       <c r="B77" s="30" t="s">
         <v>117</v>
       </c>
@@ -9600,7 +9587,7 @@
       <c r="U77" s="6"/>
     </row>
     <row r="78" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A78" s="46"/>
+      <c r="A78" s="45"/>
       <c r="B78" s="30" t="s">
         <v>118</v>
       </c>
@@ -9647,7 +9634,7 @@
       <c r="U78" s="6"/>
     </row>
     <row r="79" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A79" s="46"/>
+      <c r="A79" s="45"/>
       <c r="B79" s="30" t="s">
         <v>119</v>
       </c>
@@ -9674,7 +9661,7 @@
       <c r="U79" s="6"/>
     </row>
     <row r="80" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A80" s="46"/>
+      <c r="A80" s="45"/>
       <c r="B80" s="30" t="s">
         <v>120</v>
       </c>
@@ -9701,7 +9688,7 @@
       <c r="U80" s="6"/>
     </row>
     <row r="81" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A81" s="53">
+      <c r="A81" s="52">
         <v>12</v>
       </c>
       <c r="B81" s="28" t="s">
@@ -9732,7 +9719,7 @@
       <c r="U81" s="62"/>
     </row>
     <row r="82" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A82" s="53"/>
+      <c r="A82" s="52"/>
       <c r="B82" s="28" t="s">
         <v>123</v>
       </c>
@@ -9759,7 +9746,7 @@
       <c r="U82" s="64"/>
     </row>
     <row r="83" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A83" s="53"/>
+      <c r="A83" s="52"/>
       <c r="B83" s="28" t="s">
         <v>124</v>
       </c>
@@ -9786,7 +9773,7 @@
       <c r="U83" s="64"/>
     </row>
     <row r="84" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A84" s="53"/>
+      <c r="A84" s="52"/>
       <c r="B84" s="28" t="s">
         <v>125</v>
       </c>
@@ -9813,7 +9800,7 @@
       <c r="U84" s="64"/>
     </row>
     <row r="85" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A85" s="53"/>
+      <c r="A85" s="52"/>
       <c r="B85" s="28" t="s">
         <v>126</v>
       </c>
@@ -9840,7 +9827,7 @@
       <c r="U85" s="64"/>
     </row>
     <row r="86" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A86" s="53"/>
+      <c r="A86" s="52"/>
       <c r="B86" s="28" t="s">
         <v>127</v>
       </c>
@@ -9867,7 +9854,7 @@
       <c r="U86" s="64"/>
     </row>
     <row r="87" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A87" s="53"/>
+      <c r="A87" s="52"/>
       <c r="B87" s="28" t="s">
         <v>128</v>
       </c>
@@ -9894,7 +9881,7 @@
       <c r="U87" s="64"/>
     </row>
     <row r="88" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A88" s="46">
+      <c r="A88" s="45">
         <v>13</v>
       </c>
       <c r="B88" s="30" t="s">
@@ -9923,7 +9910,7 @@
       <c r="U88" s="64"/>
     </row>
     <row r="89" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A89" s="46"/>
+      <c r="A89" s="45"/>
       <c r="B89" s="30" t="s">
         <v>130</v>
       </c>
@@ -9950,7 +9937,7 @@
       <c r="U89" s="64"/>
     </row>
     <row r="90" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A90" s="46"/>
+      <c r="A90" s="45"/>
       <c r="B90" s="30" t="s">
         <v>131</v>
       </c>
@@ -9977,7 +9964,7 @@
       <c r="U90" s="64"/>
     </row>
     <row r="91" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A91" s="46"/>
+      <c r="A91" s="45"/>
       <c r="B91" s="30" t="s">
         <v>132</v>
       </c>
@@ -10004,7 +9991,7 @@
       <c r="U91" s="64"/>
     </row>
     <row r="92" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A92" s="46"/>
+      <c r="A92" s="45"/>
       <c r="B92" s="30" t="s">
         <v>133</v>
       </c>
@@ -10031,7 +10018,7 @@
       <c r="U92" s="64"/>
     </row>
     <row r="93" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A93" s="46"/>
+      <c r="A93" s="45"/>
       <c r="B93" s="30" t="s">
         <v>134</v>
       </c>
@@ -10058,7 +10045,7 @@
       <c r="U93" s="64"/>
     </row>
     <row r="94" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A94" s="46"/>
+      <c r="A94" s="45"/>
       <c r="B94" s="30" t="s">
         <v>135</v>
       </c>
@@ -10085,7 +10072,7 @@
       <c r="U94" s="66"/>
     </row>
     <row r="95" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A95" s="53">
+      <c r="A95" s="52">
         <v>14</v>
       </c>
       <c r="B95" s="28" t="s">
@@ -10118,7 +10105,7 @@
       <c r="U95" s="17"/>
     </row>
     <row r="96" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A96" s="53"/>
+      <c r="A96" s="52"/>
       <c r="B96" s="28" t="s">
         <v>138</v>
       </c>
@@ -10149,7 +10136,7 @@
       <c r="U96" s="17"/>
     </row>
     <row r="97" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A97" s="53"/>
+      <c r="A97" s="52"/>
       <c r="B97" s="28" t="s">
         <v>139</v>
       </c>
@@ -10180,7 +10167,7 @@
       <c r="U97" s="17"/>
     </row>
     <row r="98" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A98" s="53"/>
+      <c r="A98" s="52"/>
       <c r="B98" s="28" t="s">
         <v>140</v>
       </c>
@@ -10211,7 +10198,7 @@
       <c r="U98" s="17"/>
     </row>
     <row r="99" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A99" s="53"/>
+      <c r="A99" s="52"/>
       <c r="B99" s="28" t="s">
         <v>141</v>
       </c>
@@ -10242,7 +10229,7 @@
       <c r="U99" s="17"/>
     </row>
     <row r="100" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A100" s="53"/>
+      <c r="A100" s="52"/>
       <c r="B100" s="28" t="s">
         <v>142</v>
       </c>
@@ -10273,7 +10260,7 @@
       <c r="U100" s="17"/>
     </row>
     <row r="101" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A101" s="53"/>
+      <c r="A101" s="52"/>
       <c r="B101" s="28" t="s">
         <v>143</v>
       </c>
@@ -10304,7 +10291,7 @@
       <c r="U101" s="17"/>
     </row>
     <row r="102" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A102" s="46">
+      <c r="A102" s="45">
         <v>15</v>
       </c>
       <c r="B102" s="30" t="s">
@@ -10337,7 +10324,7 @@
       <c r="U102" s="6"/>
     </row>
     <row r="103" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A103" s="46"/>
+      <c r="A103" s="45"/>
       <c r="B103" s="30" t="s">
         <v>145</v>
       </c>
@@ -10368,7 +10355,7 @@
       <c r="U103" s="6"/>
     </row>
     <row r="104" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A104" s="46"/>
+      <c r="A104" s="45"/>
       <c r="B104" s="30" t="s">
         <v>146</v>
       </c>
@@ -10399,7 +10386,7 @@
       <c r="U104" s="6"/>
     </row>
     <row r="105" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A105" s="46"/>
+      <c r="A105" s="45"/>
       <c r="B105" s="30" t="s">
         <v>147</v>
       </c>
@@ -10430,7 +10417,7 @@
       <c r="U105" s="6"/>
     </row>
     <row r="106" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A106" s="46"/>
+      <c r="A106" s="45"/>
       <c r="B106" s="30" t="s">
         <v>148</v>
       </c>
@@ -10461,7 +10448,7 @@
       <c r="U106" s="6"/>
     </row>
     <row r="107" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A107" s="46"/>
+      <c r="A107" s="45"/>
       <c r="B107" s="30" t="s">
         <v>149</v>
       </c>
@@ -10492,7 +10479,7 @@
       <c r="U107" s="6"/>
     </row>
     <row r="108" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A108" s="46"/>
+      <c r="A108" s="45"/>
       <c r="B108" s="30" t="s">
         <v>150</v>
       </c>
@@ -10523,7 +10510,7 @@
       <c r="U108" s="6"/>
     </row>
     <row r="109" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A109" s="53">
+      <c r="A109" s="52">
         <v>16</v>
       </c>
       <c r="B109" s="28" t="s">
@@ -10556,7 +10543,7 @@
       <c r="U109" s="16"/>
     </row>
     <row r="110" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A110" s="53"/>
+      <c r="A110" s="52"/>
       <c r="B110" s="28" t="s">
         <v>152</v>
       </c>
@@ -10587,7 +10574,7 @@
       <c r="U110" s="16"/>
     </row>
     <row r="111" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A111" s="53"/>
+      <c r="A111" s="52"/>
       <c r="B111" s="28" t="s">
         <v>153</v>
       </c>
@@ -10618,7 +10605,7 @@
       <c r="U111" s="16"/>
     </row>
     <row r="112" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A112" s="53"/>
+      <c r="A112" s="52"/>
       <c r="B112" s="28" t="s">
         <v>154</v>
       </c>
@@ -10649,7 +10636,7 @@
       <c r="U112" s="16"/>
     </row>
     <row r="113" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A113" s="53"/>
+      <c r="A113" s="52"/>
       <c r="B113" s="28" t="s">
         <v>155</v>
       </c>
@@ -10680,7 +10667,7 @@
       <c r="U113" s="16"/>
     </row>
     <row r="114" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A114" s="53"/>
+      <c r="A114" s="52"/>
       <c r="B114" s="28" t="s">
         <v>156</v>
       </c>
@@ -10711,7 +10698,7 @@
       <c r="U114" s="16"/>
     </row>
     <row r="115" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A115" s="53"/>
+      <c r="A115" s="52"/>
       <c r="B115" s="28" t="s">
         <v>157</v>
       </c>
@@ -10742,7 +10729,7 @@
       <c r="U115" s="16"/>
     </row>
     <row r="116" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A116" s="46">
+      <c r="A116" s="45">
         <v>17</v>
       </c>
       <c r="B116" s="30" t="s">
@@ -10775,7 +10762,7 @@
       <c r="U116" s="6"/>
     </row>
     <row r="117" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A117" s="46"/>
+      <c r="A117" s="45"/>
       <c r="B117" s="30" t="s">
         <v>159</v>
       </c>
@@ -10806,7 +10793,7 @@
       <c r="U117" s="6"/>
     </row>
     <row r="118" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A118" s="46"/>
+      <c r="A118" s="45"/>
       <c r="B118" s="30" t="s">
         <v>160</v>
       </c>
@@ -10837,7 +10824,7 @@
       <c r="U118" s="6"/>
     </row>
     <row r="119" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A119" s="46"/>
+      <c r="A119" s="45"/>
       <c r="B119" s="30" t="s">
         <v>161</v>
       </c>
@@ -10868,7 +10855,7 @@
       <c r="U119" s="6"/>
     </row>
     <row r="120" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A120" s="46"/>
+      <c r="A120" s="45"/>
       <c r="B120" s="30" t="s">
         <v>162</v>
       </c>
@@ -10899,7 +10886,7 @@
       <c r="U120" s="6"/>
     </row>
     <row r="121" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A121" s="46"/>
+      <c r="A121" s="45"/>
       <c r="B121" s="30" t="s">
         <v>163</v>
       </c>
@@ -10930,7 +10917,7 @@
       <c r="U121" s="6"/>
     </row>
     <row r="122" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A122" s="46"/>
+      <c r="A122" s="45"/>
       <c r="B122" s="30" t="s">
         <v>164</v>
       </c>
@@ -10961,7 +10948,7 @@
       <c r="U122" s="6"/>
     </row>
     <row r="123" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A123" s="53">
+      <c r="A123" s="52">
         <v>18</v>
       </c>
       <c r="B123" s="28" t="s">
@@ -10994,7 +10981,7 @@
       <c r="U123" s="16"/>
     </row>
     <row r="124" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A124" s="53"/>
+      <c r="A124" s="52"/>
       <c r="B124" s="28" t="s">
         <v>166</v>
       </c>
@@ -11025,7 +11012,7 @@
       <c r="U124" s="16"/>
     </row>
     <row r="125" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A125" s="53"/>
+      <c r="A125" s="52"/>
       <c r="B125" s="28" t="s">
         <v>167</v>
       </c>
@@ -11056,7 +11043,7 @@
       <c r="U125" s="16"/>
     </row>
     <row r="126" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A126" s="53"/>
+      <c r="A126" s="52"/>
       <c r="B126" s="28" t="s">
         <v>168</v>
       </c>
@@ -11087,7 +11074,7 @@
       <c r="U126" s="16"/>
     </row>
     <row r="127" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A127" s="53"/>
+      <c r="A127" s="52"/>
       <c r="B127" s="27" t="s">
         <v>169</v>
       </c>
@@ -11116,7 +11103,7 @@
       <c r="U127" s="60"/>
     </row>
     <row r="128" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A128" s="53"/>
+      <c r="A128" s="52"/>
       <c r="B128" s="28" t="s">
         <v>170</v>
       </c>
@@ -11147,7 +11134,7 @@
       <c r="U128" s="16"/>
     </row>
     <row r="129" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A129" s="53"/>
+      <c r="A129" s="52"/>
       <c r="B129" s="28" t="s">
         <v>171</v>
       </c>
@@ -11178,7 +11165,7 @@
       <c r="U129" s="16"/>
     </row>
     <row r="130" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A130" s="46">
+      <c r="A130" s="45">
         <v>19</v>
       </c>
       <c r="B130" s="30" t="s">
@@ -11211,7 +11198,7 @@
       <c r="U130" s="6"/>
     </row>
     <row r="131" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A131" s="46"/>
+      <c r="A131" s="45"/>
       <c r="B131" s="30" t="s">
         <v>173</v>
       </c>
@@ -11242,7 +11229,7 @@
       <c r="U131" s="6"/>
     </row>
     <row r="132" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A132" s="46"/>
+      <c r="A132" s="45"/>
       <c r="B132" s="30" t="s">
         <v>174</v>
       </c>
@@ -11273,7 +11260,7 @@
       <c r="U132" s="6"/>
     </row>
     <row r="133" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A133" s="46"/>
+      <c r="A133" s="45"/>
       <c r="B133" s="30" t="s">
         <v>175</v>
       </c>
@@ -11304,7 +11291,7 @@
       <c r="U133" s="6"/>
     </row>
     <row r="134" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A134" s="46"/>
+      <c r="A134" s="45"/>
       <c r="B134" s="30" t="s">
         <v>176</v>
       </c>
@@ -11335,7 +11322,7 @@
       <c r="U134" s="6"/>
     </row>
     <row r="135" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A135" s="46"/>
+      <c r="A135" s="45"/>
       <c r="B135" s="30" t="s">
         <v>177</v>
       </c>
@@ -11366,7 +11353,7 @@
       <c r="U135" s="6"/>
     </row>
     <row r="136" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A136" s="46"/>
+      <c r="A136" s="45"/>
       <c r="B136" s="30" t="s">
         <v>178</v>
       </c>
@@ -11412,6 +11399,7 @@
     <row r="150" ht="20.25"/>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="A74:A80"/>
     <mergeCell ref="A123:A129"/>
     <mergeCell ref="D127:U127"/>
     <mergeCell ref="A130:A136"/>
@@ -11422,18 +11410,16 @@
     <mergeCell ref="A109:A115"/>
     <mergeCell ref="A116:A122"/>
     <mergeCell ref="A81:A87"/>
+    <mergeCell ref="M2:O2"/>
     <mergeCell ref="A46:A52"/>
     <mergeCell ref="A53:A59"/>
     <mergeCell ref="A60:A66"/>
     <mergeCell ref="A67:A73"/>
-    <mergeCell ref="A74:A80"/>
-    <mergeCell ref="J2:L2"/>
     <mergeCell ref="A4:A10"/>
     <mergeCell ref="A11:A17"/>
     <mergeCell ref="A18:A24"/>
     <mergeCell ref="A25:A31"/>
     <mergeCell ref="D29:U31"/>
-    <mergeCell ref="M2:O2"/>
     <mergeCell ref="A32:A38"/>
     <mergeCell ref="D35:U41"/>
     <mergeCell ref="A39:A45"/>
@@ -11449,6 +11435,7 @@
     <mergeCell ref="B2:C3"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
+    <mergeCell ref="J2:L2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
